--- a/samples/R8_A_県学調_答案番号整理ファイル.xlsx
+++ b/samples/R8_A_県学調_答案番号整理ファイル.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\github\survey-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9149d06814ece6b4/github/survey-dashboard/samples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2033EE3A-E66F-4EEA-A470-5CC6922D40C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{2033EE3A-E66F-4EEA-A470-5CC6922D40C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3AD4F45-5EC1-4E28-8BCA-A07D9391A4F6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1095" yWindow="5355" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="設定" sheetId="4" r:id="rId1"/>
@@ -5536,7 +5536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7287635F-B9AD-486B-B551-FBE980581C0B}">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="23.125" bestFit="1" customWidth="1"/>
@@ -5584,12 +5584,12 @@
         <v>盛岡</v>
       </c>
       <c r="M2" s="95" t="str" cm="1">
-        <f t="array" aca="1" ref="M2:M9" ca="1">IF(A5="","教育事務所未選択",_xlfn.UNIQUE(_xlfn._xlws.FILTER(INDIRECT(C2&amp;"[教育委員会名]"),INDIRECT(C2&amp;"[事務所名]")=A5)))</f>
-        <v>盛岡市</v>
+        <f t="array" aca="1" ref="M2:M5" ca="1">IF(A5="","教育事務所未選択",_xlfn.UNIQUE(_xlfn._xlws.FILTER(INDIRECT(C2&amp;"[教育委員会名]"),INDIRECT(C2&amp;"[事務所名]")=A5)))</f>
+        <v>花巻市</v>
       </c>
       <c r="N2" s="95" t="str" cm="1">
-        <f t="array" aca="1" ref="N2:N43" ca="1">IF(A8="","市町村未選択",_xlfn.UNIQUE(_xlfn._xlws.FILTER(INDIRECT(C2&amp;"["&amp;C3&amp;"]"),INDIRECT(C2&amp;"[教育委員会名]")=A8)))</f>
-        <v>盛岡市立仁王小学校</v>
+        <f t="array" aca="1" ref="N2:N16" ca="1">IF(A8="","市町村未選択",_xlfn.UNIQUE(_xlfn._xlws.FILTER(INDIRECT(C2&amp;"["&amp;C3&amp;"]"),INDIRECT(C2&amp;"[教育委員会名]")=A8)))</f>
+        <v>北上市立黒沢尻北小学校</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
@@ -5603,11 +5603,11 @@
       </c>
       <c r="M3" s="95" t="str">
         <f ca="1"/>
-        <v>岩手町</v>
+        <v>遠野市</v>
       </c>
       <c r="N3" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立城南小学校</v>
+        <v>北上市立黒沢尻東小学校</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
@@ -5623,16 +5623,16 @@
       </c>
       <c r="M4" s="95" t="str">
         <f ca="1"/>
-        <v>雫石町</v>
+        <v>北上市</v>
       </c>
       <c r="N4" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立桜城小学校</v>
+        <v>北上市立黒沢尻西小学校</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="69" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="J5" s="109" t="s">
         <v>918</v>
@@ -5643,11 +5643,11 @@
       </c>
       <c r="M5" s="95" t="str">
         <f ca="1"/>
-        <v>葛巻町</v>
+        <v>西和賀町</v>
       </c>
       <c r="N5" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立厨川小学校</v>
+        <v>北上市立東桜小学校</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
@@ -5658,13 +5658,9 @@
         <f ca="1"/>
         <v>宮古</v>
       </c>
-      <c r="M6" s="95" t="str">
-        <f ca="1"/>
-        <v>滝沢市</v>
-      </c>
       <c r="N6" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立仙北小学校</v>
+        <v>北上市立飯豊小学校</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
@@ -5678,30 +5674,22 @@
         <f ca="1"/>
         <v>県北</v>
       </c>
-      <c r="M7" s="95" t="str">
-        <f ca="1"/>
-        <v>紫波町</v>
-      </c>
       <c r="N7" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立杜陵小学校</v>
+        <v>北上市立二子小学校</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" s="69" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="L8" s="95" t="str">
         <f ca="1"/>
         <v>国独</v>
       </c>
-      <c r="M8" s="95" t="str">
-        <f ca="1"/>
-        <v>矢巾町</v>
-      </c>
       <c r="N8" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立山岸小学校</v>
+        <v>北上市立更木小学校</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
@@ -5709,13 +5697,9 @@
         <f ca="1"/>
         <v>県立</v>
       </c>
-      <c r="M9" s="95" t="str">
-        <f ca="1"/>
-        <v>八幡平市</v>
-      </c>
       <c r="N9" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立大慈寺小学校</v>
+        <v>北上市立南小学校</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
@@ -5728,22 +5712,22 @@
       </c>
       <c r="N10" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立米内小学校</v>
+        <v>北上市立鬼柳小学校</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" s="69" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="N11" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立土淵小学校</v>
+        <v>北上市立江釣子小学校</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="N12" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立中野小学校</v>
+        <v>北上市立和賀西小学校</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
@@ -5752,191 +5736,29 @@
       </c>
       <c r="N13" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立本宮小学校</v>
+        <v>北上市立笠松小学校</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" s="96" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">IFERROR(IF(A11="","学校未選択",_xlfn.XLOOKUP(A11,INDIRECT(C2&amp;"["&amp;C3&amp;"]"),INDIRECT(C2&amp;"[コード番号]"))),"選択条件が変わっています。上から順に選び直してください。")</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="N14" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立青山小学校</v>
+        <v>北上市立いわさき小学校</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="N15" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立北厨川小学校</v>
+        <v>北上市立和賀東小学校</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="N16" s="95" t="str">
         <f ca="1"/>
-        <v>盛岡市立河北小学校</v>
-      </c>
-    </row>
-    <row r="17" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N17" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立上田小学校</v>
-      </c>
-    </row>
-    <row r="18" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N18" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立山王小学校</v>
-      </c>
-    </row>
-    <row r="19" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N19" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立緑が丘小学校</v>
-      </c>
-    </row>
-    <row r="20" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N20" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立太田小学校</v>
-      </c>
-    </row>
-    <row r="21" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N21" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立太田東小学校</v>
-      </c>
-    </row>
-    <row r="22" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N22" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立城北小学校</v>
-      </c>
-    </row>
-    <row r="23" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N23" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立大新小学校</v>
-      </c>
-    </row>
-    <row r="24" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N24" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立松園小学校</v>
-      </c>
-    </row>
-    <row r="25" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N25" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立月が丘小学校</v>
-      </c>
-    </row>
-    <row r="26" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N26" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立高松小学校</v>
-      </c>
-    </row>
-    <row r="27" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N27" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立東松園小学校</v>
-      </c>
-    </row>
-    <row r="28" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N28" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立見前小学校</v>
-      </c>
-    </row>
-    <row r="29" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N29" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立飯岡小学校</v>
-      </c>
-    </row>
-    <row r="30" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N30" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立羽場小学校</v>
-      </c>
-    </row>
-    <row r="31" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N31" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立永井小学校</v>
-      </c>
-    </row>
-    <row r="32" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N32" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立手代森小学校</v>
-      </c>
-    </row>
-    <row r="33" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N33" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立津志田小学校</v>
-      </c>
-    </row>
-    <row r="34" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N34" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立向中野小学校</v>
-      </c>
-    </row>
-    <row r="35" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N35" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立見前南小学校</v>
-      </c>
-    </row>
-    <row r="36" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N36" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立都南東小学校</v>
-      </c>
-    </row>
-    <row r="37" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N37" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立北松園小学校</v>
-      </c>
-    </row>
-    <row r="38" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N38" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立玉山小学校</v>
-      </c>
-    </row>
-    <row r="39" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N39" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立渋民小学校</v>
-      </c>
-    </row>
-    <row r="40" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N40" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立巻堀小学校</v>
-      </c>
-    </row>
-    <row r="41" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N41" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市立好摩小学校</v>
-      </c>
-    </row>
-    <row r="42" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N42" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡市教育委員会</v>
-      </c>
-    </row>
-    <row r="43" spans="14:14" x14ac:dyDescent="0.4">
-      <c r="N43" s="95" t="str">
-        <f ca="1"/>
-        <v>盛岡教育事務所</v>
+        <v>北上市教育委員会</v>
       </c>
     </row>
   </sheetData>
@@ -6082,7 +5904,7 @@
       </c>
       <c r="B7">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C7" s="98" t="s">
         <v>582</v>
@@ -6092,7 +5914,7 @@
       </c>
       <c r="E7" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101001A</v>
+        <v>121114001A</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -6113,7 +5935,7 @@
       </c>
       <c r="B8">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C8" s="98" t="s">
         <v>583</v>
@@ -6123,7 +5945,7 @@
       </c>
       <c r="E8" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101002H</v>
+        <v>121114002H</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -6144,7 +5966,7 @@
       </c>
       <c r="B9">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C9" s="98" t="s">
         <v>584</v>
@@ -6154,7 +5976,7 @@
       </c>
       <c r="E9" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101003K</v>
+        <v>121114003K</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -6176,7 +5998,7 @@
       </c>
       <c r="B10">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C10" s="98" t="s">
         <v>585</v>
@@ -6186,7 +6008,7 @@
       </c>
       <c r="E10" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101004M</v>
+        <v>121114004M</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -6207,7 +6029,7 @@
       </c>
       <c r="B11">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C11" s="98" t="s">
         <v>586</v>
@@ -6217,7 +6039,7 @@
       </c>
       <c r="E11" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101005N</v>
+        <v>121114005N</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -6238,7 +6060,7 @@
       </c>
       <c r="B12">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C12" s="98" t="s">
         <v>587</v>
@@ -6248,7 +6070,7 @@
       </c>
       <c r="E12" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101006R</v>
+        <v>121114006R</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -6269,7 +6091,7 @@
       </c>
       <c r="B13">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C13" s="98" t="s">
         <v>588</v>
@@ -6279,7 +6101,7 @@
       </c>
       <c r="E13" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101007V</v>
+        <v>121114007V</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -6300,7 +6122,7 @@
       </c>
       <c r="B14">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C14" s="98" t="s">
         <v>589</v>
@@ -6310,7 +6132,7 @@
       </c>
       <c r="E14" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101008X</v>
+        <v>121114008X</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -6331,7 +6153,7 @@
       </c>
       <c r="B15">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C15" s="98" t="s">
         <v>591</v>
@@ -6341,7 +6163,7 @@
       </c>
       <c r="E15" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101009A</v>
+        <v>121114009A</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -6362,7 +6184,7 @@
       </c>
       <c r="B16">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C16" s="98" t="s">
         <v>592</v>
@@ -6372,7 +6194,7 @@
       </c>
       <c r="E16" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101010H</v>
+        <v>121114010H</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -6393,7 +6215,7 @@
       </c>
       <c r="B17">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C17" s="98" t="s">
         <v>593</v>
@@ -6403,7 +6225,7 @@
       </c>
       <c r="E17" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101011K</v>
+        <v>121114011K</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -6424,7 +6246,7 @@
       </c>
       <c r="B18">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C18" s="98" t="s">
         <v>594</v>
@@ -6434,7 +6256,7 @@
       </c>
       <c r="E18" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101012M</v>
+        <v>121114012M</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -6455,7 +6277,7 @@
       </c>
       <c r="B19">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C19" s="98" t="s">
         <v>595</v>
@@ -6465,7 +6287,7 @@
       </c>
       <c r="E19" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101013N</v>
+        <v>121114013N</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -6486,7 +6308,7 @@
       </c>
       <c r="B20">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C20" s="98" t="s">
         <v>596</v>
@@ -6496,7 +6318,7 @@
       </c>
       <c r="E20" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101014R</v>
+        <v>121114014R</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -6517,7 +6339,7 @@
       </c>
       <c r="B21">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C21" s="98" t="s">
         <v>597</v>
@@ -6527,7 +6349,7 @@
       </c>
       <c r="E21" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101015V</v>
+        <v>121114015V</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -6548,7 +6370,7 @@
       </c>
       <c r="B22">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C22" s="98" t="s">
         <v>598</v>
@@ -6558,7 +6380,7 @@
       </c>
       <c r="E22" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101016X</v>
+        <v>121114016X</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -6579,7 +6401,7 @@
       </c>
       <c r="B23">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C23" s="98" t="s">
         <v>599</v>
@@ -6589,7 +6411,7 @@
       </c>
       <c r="E23" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101017A</v>
+        <v>121114017A</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -6610,7 +6432,7 @@
       </c>
       <c r="B24">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C24" s="98" t="s">
         <v>600</v>
@@ -6620,7 +6442,7 @@
       </c>
       <c r="E24" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101018H</v>
+        <v>121114018H</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -6641,7 +6463,7 @@
       </c>
       <c r="B25">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C25" s="98" t="s">
         <v>601</v>
@@ -6651,7 +6473,7 @@
       </c>
       <c r="E25" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101019K</v>
+        <v>121114019K</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -6672,7 +6494,7 @@
       </c>
       <c r="B26">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C26" s="98" t="s">
         <v>602</v>
@@ -6682,7 +6504,7 @@
       </c>
       <c r="E26" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101020M</v>
+        <v>121114020M</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -6703,7 +6525,7 @@
       </c>
       <c r="B27">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C27" s="98" t="s">
         <v>603</v>
@@ -6713,7 +6535,7 @@
       </c>
       <c r="E27" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101021N</v>
+        <v>121114021N</v>
       </c>
       <c r="I27" s="106"/>
     </row>
@@ -6723,7 +6545,7 @@
       </c>
       <c r="B28">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C28" s="98" t="s">
         <v>604</v>
@@ -6733,7 +6555,7 @@
       </c>
       <c r="E28" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101022R</v>
+        <v>121114022R</v>
       </c>
       <c r="I28" s="106"/>
     </row>
@@ -6743,7 +6565,7 @@
       </c>
       <c r="B29">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C29" s="98" t="s">
         <v>605</v>
@@ -6753,7 +6575,7 @@
       </c>
       <c r="E29" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101023V</v>
+        <v>121114023V</v>
       </c>
       <c r="I29" s="106"/>
     </row>
@@ -6763,7 +6585,7 @@
       </c>
       <c r="B30">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C30" s="98" t="s">
         <v>606</v>
@@ -6773,7 +6595,7 @@
       </c>
       <c r="E30" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101024X</v>
+        <v>121114024X</v>
       </c>
       <c r="I30" s="106"/>
     </row>
@@ -6783,7 +6605,7 @@
       </c>
       <c r="B31">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C31" s="98" t="s">
         <v>607</v>
@@ -6793,7 +6615,7 @@
       </c>
       <c r="E31" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101025A</v>
+        <v>121114025A</v>
       </c>
       <c r="I31" s="106"/>
     </row>
@@ -6803,7 +6625,7 @@
       </c>
       <c r="B32">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C32" s="98" t="s">
         <v>608</v>
@@ -6813,7 +6635,7 @@
       </c>
       <c r="E32" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101026H</v>
+        <v>121114026H</v>
       </c>
       <c r="I32" s="106"/>
     </row>
@@ -6823,7 +6645,7 @@
       </c>
       <c r="B33">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C33" s="98" t="s">
         <v>609</v>
@@ -6833,7 +6655,7 @@
       </c>
       <c r="E33" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101027K</v>
+        <v>121114027K</v>
       </c>
       <c r="I33" s="106"/>
     </row>
@@ -6843,7 +6665,7 @@
       </c>
       <c r="B34">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C34" s="98" t="s">
         <v>610</v>
@@ -6853,7 +6675,7 @@
       </c>
       <c r="E34" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101028M</v>
+        <v>121114028M</v>
       </c>
       <c r="I34" s="106"/>
     </row>
@@ -6863,7 +6685,7 @@
       </c>
       <c r="B35">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C35" s="98" t="s">
         <v>611</v>
@@ -6873,7 +6695,7 @@
       </c>
       <c r="E35" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101029N</v>
+        <v>121114029N</v>
       </c>
       <c r="I35" s="106"/>
     </row>
@@ -6883,7 +6705,7 @@
       </c>
       <c r="B36">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C36" s="98" t="s">
         <v>612</v>
@@ -6893,7 +6715,7 @@
       </c>
       <c r="E36" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101030R</v>
+        <v>121114030R</v>
       </c>
       <c r="I36" s="106"/>
     </row>
@@ -6903,7 +6725,7 @@
       </c>
       <c r="B37">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C37" s="98" t="s">
         <v>613</v>
@@ -6913,7 +6735,7 @@
       </c>
       <c r="E37" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101031V</v>
+        <v>121114031V</v>
       </c>
       <c r="I37" s="106"/>
     </row>
@@ -6923,7 +6745,7 @@
       </c>
       <c r="B38">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C38" s="98" t="s">
         <v>614</v>
@@ -6933,7 +6755,7 @@
       </c>
       <c r="E38" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101032X</v>
+        <v>121114032X</v>
       </c>
       <c r="I38" s="106"/>
     </row>
@@ -6943,7 +6765,7 @@
       </c>
       <c r="B39">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C39" s="98" t="s">
         <v>615</v>
@@ -6953,7 +6775,7 @@
       </c>
       <c r="E39" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101033A</v>
+        <v>121114033A</v>
       </c>
       <c r="I39" s="106"/>
     </row>
@@ -6963,7 +6785,7 @@
       </c>
       <c r="B40">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C40" s="98" t="s">
         <v>616</v>
@@ -6973,7 +6795,7 @@
       </c>
       <c r="E40" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101034H</v>
+        <v>121114034H</v>
       </c>
       <c r="I40" s="106"/>
     </row>
@@ -6983,7 +6805,7 @@
       </c>
       <c r="B41">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C41" s="98" t="s">
         <v>617</v>
@@ -6993,7 +6815,7 @@
       </c>
       <c r="E41" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101035K</v>
+        <v>121114035K</v>
       </c>
       <c r="I41" s="106"/>
     </row>
@@ -7003,7 +6825,7 @@
       </c>
       <c r="B42">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C42" s="98" t="s">
         <v>618</v>
@@ -7013,7 +6835,7 @@
       </c>
       <c r="E42" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101036M</v>
+        <v>121114036M</v>
       </c>
       <c r="I42" s="106"/>
     </row>
@@ -7023,7 +6845,7 @@
       </c>
       <c r="B43">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C43" s="98" t="s">
         <v>619</v>
@@ -7033,7 +6855,7 @@
       </c>
       <c r="E43" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101037N</v>
+        <v>121114037N</v>
       </c>
       <c r="I43" s="106"/>
     </row>
@@ -7043,7 +6865,7 @@
       </c>
       <c r="B44">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C44" s="98" t="s">
         <v>620</v>
@@ -7053,7 +6875,7 @@
       </c>
       <c r="E44" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101038R</v>
+        <v>121114038R</v>
       </c>
       <c r="I44" s="106"/>
     </row>
@@ -7063,7 +6885,7 @@
       </c>
       <c r="B45">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C45" s="98" t="s">
         <v>621</v>
@@ -7073,7 +6895,7 @@
       </c>
       <c r="E45" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101039V</v>
+        <v>121114039V</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -7083,7 +6905,7 @@
       </c>
       <c r="B46">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C46" s="98" t="s">
         <v>622</v>
@@ -7093,7 +6915,7 @@
       </c>
       <c r="E46" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101040X</v>
+        <v>121114040X</v>
       </c>
       <c r="I46" s="106"/>
     </row>
@@ -7103,7 +6925,7 @@
       </c>
       <c r="B47">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C47" s="98" t="s">
         <v>623</v>
@@ -7113,7 +6935,7 @@
       </c>
       <c r="E47" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101041A</v>
+        <v>121114041A</v>
       </c>
       <c r="I47" s="106"/>
     </row>
@@ -7123,7 +6945,7 @@
       </c>
       <c r="B48">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C48" s="98" t="s">
         <v>624</v>
@@ -7133,7 +6955,7 @@
       </c>
       <c r="E48" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101042H</v>
+        <v>121114042H</v>
       </c>
       <c r="I48" s="106"/>
     </row>
@@ -7143,7 +6965,7 @@
       </c>
       <c r="B49">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C49" s="98" t="s">
         <v>625</v>
@@ -7153,7 +6975,7 @@
       </c>
       <c r="E49" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101043K</v>
+        <v>121114043K</v>
       </c>
       <c r="I49" s="106"/>
     </row>
@@ -7163,7 +6985,7 @@
       </c>
       <c r="B50">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C50" s="98" t="s">
         <v>626</v>
@@ -7173,7 +6995,7 @@
       </c>
       <c r="E50" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101044M</v>
+        <v>121114044M</v>
       </c>
       <c r="I50" s="106"/>
     </row>
@@ -7183,7 +7005,7 @@
       </c>
       <c r="B51">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C51" s="98" t="s">
         <v>627</v>
@@ -7193,7 +7015,7 @@
       </c>
       <c r="E51" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101045N</v>
+        <v>121114045N</v>
       </c>
       <c r="I51" s="106"/>
     </row>
@@ -7203,7 +7025,7 @@
       </c>
       <c r="B52">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C52" s="98" t="s">
         <v>628</v>
@@ -7213,7 +7035,7 @@
       </c>
       <c r="E52" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101046R</v>
+        <v>121114046R</v>
       </c>
       <c r="I52" s="106"/>
     </row>
@@ -7223,7 +7045,7 @@
       </c>
       <c r="B53">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C53" s="98" t="s">
         <v>629</v>
@@ -7233,7 +7055,7 @@
       </c>
       <c r="E53" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101047V</v>
+        <v>121114047V</v>
       </c>
       <c r="I53" s="106"/>
     </row>
@@ -7243,7 +7065,7 @@
       </c>
       <c r="B54">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C54" s="98" t="s">
         <v>630</v>
@@ -7253,7 +7075,7 @@
       </c>
       <c r="E54" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101048X</v>
+        <v>121114048X</v>
       </c>
       <c r="I54" s="106"/>
     </row>
@@ -7263,7 +7085,7 @@
       </c>
       <c r="B55">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C55" s="98" t="s">
         <v>631</v>
@@ -7273,7 +7095,7 @@
       </c>
       <c r="E55" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101049A</v>
+        <v>121114049A</v>
       </c>
       <c r="I55" s="106"/>
     </row>
@@ -7283,7 +7105,7 @@
       </c>
       <c r="B56">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C56" s="98" t="s">
         <v>632</v>
@@ -7293,7 +7115,7 @@
       </c>
       <c r="E56" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101050H</v>
+        <v>121114050H</v>
       </c>
       <c r="I56" s="106"/>
     </row>
@@ -7303,7 +7125,7 @@
       </c>
       <c r="B57">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C57" s="98" t="s">
         <v>633</v>
@@ -7313,7 +7135,7 @@
       </c>
       <c r="E57" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101051K</v>
+        <v>121114051K</v>
       </c>
       <c r="I57" s="106"/>
     </row>
@@ -7323,7 +7145,7 @@
       </c>
       <c r="B58">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C58" s="98" t="s">
         <v>634</v>
@@ -7333,7 +7155,7 @@
       </c>
       <c r="E58" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101052M</v>
+        <v>121114052M</v>
       </c>
       <c r="I58" s="106"/>
     </row>
@@ -7343,7 +7165,7 @@
       </c>
       <c r="B59">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C59" s="98" t="s">
         <v>635</v>
@@ -7353,7 +7175,7 @@
       </c>
       <c r="E59" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101053N</v>
+        <v>121114053N</v>
       </c>
       <c r="I59" s="106"/>
     </row>
@@ -7363,7 +7185,7 @@
       </c>
       <c r="B60">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C60" s="98" t="s">
         <v>636</v>
@@ -7373,7 +7195,7 @@
       </c>
       <c r="E60" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101054R</v>
+        <v>121114054R</v>
       </c>
       <c r="I60" s="106"/>
     </row>
@@ -7383,7 +7205,7 @@
       </c>
       <c r="B61">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C61" s="98" t="s">
         <v>637</v>
@@ -7393,7 +7215,7 @@
       </c>
       <c r="E61" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101055V</v>
+        <v>121114055V</v>
       </c>
       <c r="I61" s="106"/>
     </row>
@@ -7403,7 +7225,7 @@
       </c>
       <c r="B62">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C62" s="98" t="s">
         <v>638</v>
@@ -7413,7 +7235,7 @@
       </c>
       <c r="E62" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101056X</v>
+        <v>121114056X</v>
       </c>
       <c r="I62" s="106"/>
     </row>
@@ -7423,7 +7245,7 @@
       </c>
       <c r="B63">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C63" s="98" t="s">
         <v>639</v>
@@ -7433,7 +7255,7 @@
       </c>
       <c r="E63" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101057A</v>
+        <v>121114057A</v>
       </c>
       <c r="I63" s="106"/>
     </row>
@@ -7443,7 +7265,7 @@
       </c>
       <c r="B64">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C64" s="98" t="s">
         <v>640</v>
@@ -7453,7 +7275,7 @@
       </c>
       <c r="E64" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101058H</v>
+        <v>121114058H</v>
       </c>
       <c r="I64" s="106"/>
     </row>
@@ -7463,7 +7285,7 @@
       </c>
       <c r="B65">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C65" s="98" t="s">
         <v>641</v>
@@ -7473,7 +7295,7 @@
       </c>
       <c r="E65" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101059K</v>
+        <v>121114059K</v>
       </c>
       <c r="I65" s="106"/>
     </row>
@@ -7483,7 +7305,7 @@
       </c>
       <c r="B66">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C66" s="98" t="s">
         <v>642</v>
@@ -7493,7 +7315,7 @@
       </c>
       <c r="E66" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101060M</v>
+        <v>121114060M</v>
       </c>
       <c r="I66" s="106"/>
     </row>
@@ -7503,7 +7325,7 @@
       </c>
       <c r="B67">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C67" s="98" t="s">
         <v>643</v>
@@ -7513,7 +7335,7 @@
       </c>
       <c r="E67" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101061N</v>
+        <v>121114061N</v>
       </c>
       <c r="I67" s="106"/>
     </row>
@@ -7523,7 +7345,7 @@
       </c>
       <c r="B68">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C68" s="98" t="s">
         <v>644</v>
@@ -7533,7 +7355,7 @@
       </c>
       <c r="E68" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101062R</v>
+        <v>121114062R</v>
       </c>
       <c r="I68" s="106"/>
     </row>
@@ -7543,7 +7365,7 @@
       </c>
       <c r="B69">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C69" s="98" t="s">
         <v>645</v>
@@ -7553,7 +7375,7 @@
       </c>
       <c r="E69" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101063V</v>
+        <v>121114063V</v>
       </c>
       <c r="I69" s="106"/>
     </row>
@@ -7563,7 +7385,7 @@
       </c>
       <c r="B70">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C70" s="98" t="s">
         <v>646</v>
@@ -7573,7 +7395,7 @@
       </c>
       <c r="E70" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101064X</v>
+        <v>121114064X</v>
       </c>
       <c r="I70" s="106"/>
     </row>
@@ -7583,7 +7405,7 @@
       </c>
       <c r="B71">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C71" s="98" t="s">
         <v>647</v>
@@ -7593,7 +7415,7 @@
       </c>
       <c r="E71" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101065A</v>
+        <v>121114065A</v>
       </c>
       <c r="I71" s="106"/>
     </row>
@@ -7603,7 +7425,7 @@
       </c>
       <c r="B72">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C72" s="98" t="s">
         <v>648</v>
@@ -7613,7 +7435,7 @@
       </c>
       <c r="E72" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101066H</v>
+        <v>121114066H</v>
       </c>
       <c r="I72" s="106"/>
     </row>
@@ -7623,7 +7445,7 @@
       </c>
       <c r="B73">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C73" s="98" t="s">
         <v>649</v>
@@ -7633,7 +7455,7 @@
       </c>
       <c r="E73" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101067K</v>
+        <v>121114067K</v>
       </c>
       <c r="I73" s="106"/>
     </row>
@@ -7643,7 +7465,7 @@
       </c>
       <c r="B74">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C74" s="98" t="s">
         <v>650</v>
@@ -7653,7 +7475,7 @@
       </c>
       <c r="E74" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101068M</v>
+        <v>121114068M</v>
       </c>
       <c r="I74" s="106"/>
     </row>
@@ -7663,7 +7485,7 @@
       </c>
       <c r="B75">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C75" s="98" t="s">
         <v>651</v>
@@ -7673,7 +7495,7 @@
       </c>
       <c r="E75" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101069N</v>
+        <v>121114069N</v>
       </c>
       <c r="I75" s="106"/>
     </row>
@@ -7683,7 +7505,7 @@
       </c>
       <c r="B76">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C76" s="98" t="s">
         <v>652</v>
@@ -7693,7 +7515,7 @@
       </c>
       <c r="E76" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101070R</v>
+        <v>121114070R</v>
       </c>
       <c r="I76" s="106"/>
     </row>
@@ -7703,7 +7525,7 @@
       </c>
       <c r="B77">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C77" s="98" t="s">
         <v>653</v>
@@ -7713,7 +7535,7 @@
       </c>
       <c r="E77" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101071V</v>
+        <v>121114071V</v>
       </c>
       <c r="I77" s="106"/>
     </row>
@@ -7723,7 +7545,7 @@
       </c>
       <c r="B78">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C78" s="98" t="s">
         <v>654</v>
@@ -7733,7 +7555,7 @@
       </c>
       <c r="E78" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101072X</v>
+        <v>121114072X</v>
       </c>
       <c r="I78" s="106"/>
     </row>
@@ -7743,7 +7565,7 @@
       </c>
       <c r="B79">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C79" s="98" t="s">
         <v>655</v>
@@ -7753,7 +7575,7 @@
       </c>
       <c r="E79" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101073A</v>
+        <v>121114073A</v>
       </c>
       <c r="I79" s="106"/>
     </row>
@@ -7763,7 +7585,7 @@
       </c>
       <c r="B80">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C80" s="98" t="s">
         <v>656</v>
@@ -7773,7 +7595,7 @@
       </c>
       <c r="E80" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101074H</v>
+        <v>121114074H</v>
       </c>
       <c r="I80" s="106"/>
     </row>
@@ -7783,7 +7605,7 @@
       </c>
       <c r="B81">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C81" s="98" t="s">
         <v>657</v>
@@ -7793,7 +7615,7 @@
       </c>
       <c r="E81" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101075K</v>
+        <v>121114075K</v>
       </c>
       <c r="I81" s="106"/>
     </row>
@@ -7803,7 +7625,7 @@
       </c>
       <c r="B82">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C82" s="98" t="s">
         <v>658</v>
@@ -7813,7 +7635,7 @@
       </c>
       <c r="E82" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101076M</v>
+        <v>121114076M</v>
       </c>
       <c r="I82" s="106"/>
     </row>
@@ -7823,7 +7645,7 @@
       </c>
       <c r="B83">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C83" s="98" t="s">
         <v>659</v>
@@ -7833,7 +7655,7 @@
       </c>
       <c r="E83" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101077N</v>
+        <v>121114077N</v>
       </c>
       <c r="I83" s="106"/>
     </row>
@@ -7843,7 +7665,7 @@
       </c>
       <c r="B84">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C84" s="98" t="s">
         <v>660</v>
@@ -7853,7 +7675,7 @@
       </c>
       <c r="E84" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101078R</v>
+        <v>121114078R</v>
       </c>
       <c r="I84" s="106"/>
     </row>
@@ -7863,7 +7685,7 @@
       </c>
       <c r="B85">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C85" s="98" t="s">
         <v>661</v>
@@ -7873,7 +7695,7 @@
       </c>
       <c r="E85" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101079V</v>
+        <v>121114079V</v>
       </c>
       <c r="I85" s="106"/>
     </row>
@@ -7883,7 +7705,7 @@
       </c>
       <c r="B86">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C86" s="98" t="s">
         <v>662</v>
@@ -7893,7 +7715,7 @@
       </c>
       <c r="E86" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101080X</v>
+        <v>121114080X</v>
       </c>
       <c r="I86" s="106"/>
     </row>
@@ -7903,7 +7725,7 @@
       </c>
       <c r="B87">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C87" s="98" t="s">
         <v>663</v>
@@ -7913,7 +7735,7 @@
       </c>
       <c r="E87" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101081A</v>
+        <v>121114081A</v>
       </c>
       <c r="I87" s="106"/>
     </row>
@@ -7923,7 +7745,7 @@
       </c>
       <c r="B88">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C88" s="98" t="s">
         <v>664</v>
@@ -7933,7 +7755,7 @@
       </c>
       <c r="E88" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101082H</v>
+        <v>121114082H</v>
       </c>
       <c r="I88" s="106"/>
     </row>
@@ -7943,7 +7765,7 @@
       </c>
       <c r="B89">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C89" s="98" t="s">
         <v>665</v>
@@ -7953,7 +7775,7 @@
       </c>
       <c r="E89" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101083K</v>
+        <v>121114083K</v>
       </c>
       <c r="I89" s="106"/>
     </row>
@@ -7963,7 +7785,7 @@
       </c>
       <c r="B90">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C90" s="98" t="s">
         <v>666</v>
@@ -7973,7 +7795,7 @@
       </c>
       <c r="E90" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101084M</v>
+        <v>121114084M</v>
       </c>
       <c r="I90" s="106"/>
     </row>
@@ -7983,7 +7805,7 @@
       </c>
       <c r="B91">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C91" s="98" t="s">
         <v>667</v>
@@ -7993,7 +7815,7 @@
       </c>
       <c r="E91" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101085N</v>
+        <v>121114085N</v>
       </c>
       <c r="I91" s="106"/>
     </row>
@@ -8003,7 +7825,7 @@
       </c>
       <c r="B92">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C92" s="98" t="s">
         <v>668</v>
@@ -8013,7 +7835,7 @@
       </c>
       <c r="E92" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101086R</v>
+        <v>121114086R</v>
       </c>
       <c r="I92" s="106"/>
     </row>
@@ -8023,7 +7845,7 @@
       </c>
       <c r="B93">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C93" s="98" t="s">
         <v>669</v>
@@ -8033,7 +7855,7 @@
       </c>
       <c r="E93" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101087V</v>
+        <v>121114087V</v>
       </c>
       <c r="I93" s="106"/>
     </row>
@@ -8043,7 +7865,7 @@
       </c>
       <c r="B94">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C94" s="98" t="s">
         <v>670</v>
@@ -8053,7 +7875,7 @@
       </c>
       <c r="E94" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101088X</v>
+        <v>121114088X</v>
       </c>
       <c r="I94" s="106"/>
     </row>
@@ -8063,7 +7885,7 @@
       </c>
       <c r="B95">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C95" s="98" t="s">
         <v>671</v>
@@ -8073,7 +7895,7 @@
       </c>
       <c r="E95" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101089A</v>
+        <v>121114089A</v>
       </c>
       <c r="I95" s="106"/>
     </row>
@@ -8083,7 +7905,7 @@
       </c>
       <c r="B96">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C96" s="98" t="s">
         <v>672</v>
@@ -8093,7 +7915,7 @@
       </c>
       <c r="E96" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101090H</v>
+        <v>121114090H</v>
       </c>
       <c r="I96" s="106"/>
     </row>
@@ -8103,7 +7925,7 @@
       </c>
       <c r="B97">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C97" s="98" t="s">
         <v>673</v>
@@ -8113,7 +7935,7 @@
       </c>
       <c r="E97" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101091K</v>
+        <v>121114091K</v>
       </c>
       <c r="I97" s="106"/>
     </row>
@@ -8123,7 +7945,7 @@
       </c>
       <c r="B98">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C98" s="98" t="s">
         <v>674</v>
@@ -8133,7 +7955,7 @@
       </c>
       <c r="E98" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101092M</v>
+        <v>121114092M</v>
       </c>
       <c r="I98" s="106"/>
     </row>
@@ -8143,7 +7965,7 @@
       </c>
       <c r="B99">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C99" s="98" t="s">
         <v>675</v>
@@ -8153,7 +7975,7 @@
       </c>
       <c r="E99" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101093N</v>
+        <v>121114093N</v>
       </c>
       <c r="I99" s="106"/>
     </row>
@@ -8163,7 +7985,7 @@
       </c>
       <c r="B100">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C100" s="98" t="s">
         <v>676</v>
@@ -8173,7 +7995,7 @@
       </c>
       <c r="E100" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101094R</v>
+        <v>121114094R</v>
       </c>
       <c r="I100" s="106"/>
     </row>
@@ -8183,7 +8005,7 @@
       </c>
       <c r="B101">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C101" s="98" t="s">
         <v>677</v>
@@ -8193,7 +8015,7 @@
       </c>
       <c r="E101" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101095V</v>
+        <v>121114095V</v>
       </c>
       <c r="I101" s="106"/>
     </row>
@@ -8203,7 +8025,7 @@
       </c>
       <c r="B102">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C102" s="98" t="s">
         <v>678</v>
@@ -8213,7 +8035,7 @@
       </c>
       <c r="E102" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101096X</v>
+        <v>121114096X</v>
       </c>
       <c r="I102" s="106"/>
     </row>
@@ -8223,7 +8045,7 @@
       </c>
       <c r="B103">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C103" s="98" t="s">
         <v>679</v>
@@ -8233,7 +8055,7 @@
       </c>
       <c r="E103" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101097A</v>
+        <v>121114097A</v>
       </c>
       <c r="I103" s="106"/>
     </row>
@@ -8243,7 +8065,7 @@
       </c>
       <c r="B104">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C104" s="98" t="s">
         <v>680</v>
@@ -8253,7 +8075,7 @@
       </c>
       <c r="E104" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101098H</v>
+        <v>121114098H</v>
       </c>
       <c r="I104" s="106"/>
     </row>
@@ -8263,7 +8085,7 @@
       </c>
       <c r="B105">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C105" s="98" t="s">
         <v>681</v>
@@ -8273,7 +8095,7 @@
       </c>
       <c r="E105" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101099K</v>
+        <v>121114099K</v>
       </c>
       <c r="I105" s="106"/>
     </row>
@@ -8283,7 +8105,7 @@
       </c>
       <c r="B106">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C106" s="98" t="s">
         <v>682</v>
@@ -8293,7 +8115,7 @@
       </c>
       <c r="E106" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101100M</v>
+        <v>121114100M</v>
       </c>
       <c r="I106" s="106"/>
     </row>
@@ -8303,7 +8125,7 @@
       </c>
       <c r="B107">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C107" s="98" t="s">
         <v>683</v>
@@ -8313,7 +8135,7 @@
       </c>
       <c r="E107" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101101N</v>
+        <v>121114101N</v>
       </c>
       <c r="I107" s="106"/>
     </row>
@@ -8323,7 +8145,7 @@
       </c>
       <c r="B108">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C108" s="98" t="s">
         <v>684</v>
@@ -8333,7 +8155,7 @@
       </c>
       <c r="E108" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101102R</v>
+        <v>121114102R</v>
       </c>
       <c r="I108" s="106"/>
     </row>
@@ -8343,7 +8165,7 @@
       </c>
       <c r="B109">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C109" s="98" t="s">
         <v>685</v>
@@ -8353,7 +8175,7 @@
       </c>
       <c r="E109" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101103V</v>
+        <v>121114103V</v>
       </c>
       <c r="I109" s="106"/>
     </row>
@@ -8363,7 +8185,7 @@
       </c>
       <c r="B110">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C110" s="98" t="s">
         <v>686</v>
@@ -8373,7 +8195,7 @@
       </c>
       <c r="E110" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101104X</v>
+        <v>121114104X</v>
       </c>
       <c r="I110" s="106"/>
     </row>
@@ -8383,7 +8205,7 @@
       </c>
       <c r="B111">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C111" s="98" t="s">
         <v>687</v>
@@ -8393,7 +8215,7 @@
       </c>
       <c r="E111" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101105A</v>
+        <v>121114105A</v>
       </c>
       <c r="I111" s="106"/>
     </row>
@@ -8403,7 +8225,7 @@
       </c>
       <c r="B112">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C112" s="98" t="s">
         <v>688</v>
@@ -8413,7 +8235,7 @@
       </c>
       <c r="E112" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101106H</v>
+        <v>121114106H</v>
       </c>
       <c r="I112" s="106"/>
     </row>
@@ -8423,7 +8245,7 @@
       </c>
       <c r="B113">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C113" s="98" t="s">
         <v>689</v>
@@ -8433,7 +8255,7 @@
       </c>
       <c r="E113" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101107K</v>
+        <v>121114107K</v>
       </c>
       <c r="I113" s="106"/>
     </row>
@@ -8443,7 +8265,7 @@
       </c>
       <c r="B114">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C114" s="98" t="s">
         <v>690</v>
@@ -8453,7 +8275,7 @@
       </c>
       <c r="E114" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101108M</v>
+        <v>121114108M</v>
       </c>
       <c r="I114" s="106"/>
     </row>
@@ -8463,7 +8285,7 @@
       </c>
       <c r="B115">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C115" s="98" t="s">
         <v>691</v>
@@ -8473,7 +8295,7 @@
       </c>
       <c r="E115" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101109N</v>
+        <v>121114109N</v>
       </c>
       <c r="I115" s="106"/>
     </row>
@@ -8483,7 +8305,7 @@
       </c>
       <c r="B116">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C116" s="98" t="s">
         <v>692</v>
@@ -8493,7 +8315,7 @@
       </c>
       <c r="E116" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101110R</v>
+        <v>121114110R</v>
       </c>
       <c r="I116" s="106"/>
     </row>
@@ -8503,7 +8325,7 @@
       </c>
       <c r="B117">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C117" s="98" t="s">
         <v>693</v>
@@ -8513,7 +8335,7 @@
       </c>
       <c r="E117" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101111V</v>
+        <v>121114111V</v>
       </c>
       <c r="I117" s="106"/>
     </row>
@@ -8523,7 +8345,7 @@
       </c>
       <c r="B118">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C118" s="98" t="s">
         <v>694</v>
@@ -8533,7 +8355,7 @@
       </c>
       <c r="E118" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101112X</v>
+        <v>121114112X</v>
       </c>
       <c r="I118" s="106"/>
     </row>
@@ -8543,7 +8365,7 @@
       </c>
       <c r="B119">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C119" s="98" t="s">
         <v>695</v>
@@ -8553,7 +8375,7 @@
       </c>
       <c r="E119" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101113A</v>
+        <v>121114113A</v>
       </c>
       <c r="I119" s="106"/>
     </row>
@@ -8563,7 +8385,7 @@
       </c>
       <c r="B120">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C120" s="98" t="s">
         <v>696</v>
@@ -8573,7 +8395,7 @@
       </c>
       <c r="E120" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101114H</v>
+        <v>121114114H</v>
       </c>
       <c r="I120" s="106"/>
     </row>
@@ -8583,7 +8405,7 @@
       </c>
       <c r="B121">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C121" s="98" t="s">
         <v>697</v>
@@ -8593,7 +8415,7 @@
       </c>
       <c r="E121" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101115K</v>
+        <v>121114115K</v>
       </c>
       <c r="I121" s="106"/>
     </row>
@@ -8603,7 +8425,7 @@
       </c>
       <c r="B122">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C122" s="98" t="s">
         <v>698</v>
@@ -8613,7 +8435,7 @@
       </c>
       <c r="E122" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101116M</v>
+        <v>121114116M</v>
       </c>
       <c r="I122" s="106"/>
     </row>
@@ -8623,7 +8445,7 @@
       </c>
       <c r="B123">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C123" s="98" t="s">
         <v>699</v>
@@ -8633,7 +8455,7 @@
       </c>
       <c r="E123" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101117N</v>
+        <v>121114117N</v>
       </c>
       <c r="I123" s="106"/>
     </row>
@@ -8643,7 +8465,7 @@
       </c>
       <c r="B124">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C124" s="98" t="s">
         <v>700</v>
@@ -8653,7 +8475,7 @@
       </c>
       <c r="E124" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101118R</v>
+        <v>121114118R</v>
       </c>
       <c r="I124" s="106"/>
     </row>
@@ -8663,7 +8485,7 @@
       </c>
       <c r="B125">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C125" s="98" t="s">
         <v>701</v>
@@ -8673,7 +8495,7 @@
       </c>
       <c r="E125" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101119V</v>
+        <v>121114119V</v>
       </c>
       <c r="I125" s="106"/>
     </row>
@@ -8683,7 +8505,7 @@
       </c>
       <c r="B126">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C126" s="98" t="s">
         <v>702</v>
@@ -8693,7 +8515,7 @@
       </c>
       <c r="E126" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101120X</v>
+        <v>121114120X</v>
       </c>
       <c r="I126" s="106"/>
     </row>
@@ -8703,7 +8525,7 @@
       </c>
       <c r="B127">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C127" s="98" t="s">
         <v>703</v>
@@ -8713,7 +8535,7 @@
       </c>
       <c r="E127" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101121A</v>
+        <v>121114121A</v>
       </c>
       <c r="I127" s="106"/>
     </row>
@@ -8723,7 +8545,7 @@
       </c>
       <c r="B128">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C128" s="98" t="s">
         <v>704</v>
@@ -8733,7 +8555,7 @@
       </c>
       <c r="E128" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101122H</v>
+        <v>121114122H</v>
       </c>
       <c r="I128" s="106"/>
     </row>
@@ -8743,7 +8565,7 @@
       </c>
       <c r="B129">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C129" s="98" t="s">
         <v>705</v>
@@ -8753,7 +8575,7 @@
       </c>
       <c r="E129" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101123K</v>
+        <v>121114123K</v>
       </c>
       <c r="I129" s="106"/>
     </row>
@@ -8763,7 +8585,7 @@
       </c>
       <c r="B130">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C130" s="98" t="s">
         <v>706</v>
@@ -8773,7 +8595,7 @@
       </c>
       <c r="E130" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101124M</v>
+        <v>121114124M</v>
       </c>
       <c r="I130" s="106"/>
     </row>
@@ -8783,7 +8605,7 @@
       </c>
       <c r="B131">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C131" s="98" t="s">
         <v>707</v>
@@ -8793,7 +8615,7 @@
       </c>
       <c r="E131" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101125N</v>
+        <v>121114125N</v>
       </c>
       <c r="I131" s="106"/>
     </row>
@@ -8803,7 +8625,7 @@
       </c>
       <c r="B132">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C132" s="98" t="s">
         <v>708</v>
@@ -8813,7 +8635,7 @@
       </c>
       <c r="E132" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101126R</v>
+        <v>121114126R</v>
       </c>
       <c r="I132" s="106"/>
     </row>
@@ -8823,7 +8645,7 @@
       </c>
       <c r="B133">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C133" s="98" t="s">
         <v>709</v>
@@ -8833,7 +8655,7 @@
       </c>
       <c r="E133" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101127V</v>
+        <v>121114127V</v>
       </c>
       <c r="I133" s="106"/>
     </row>
@@ -8843,7 +8665,7 @@
       </c>
       <c r="B134">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C134" s="98" t="s">
         <v>710</v>
@@ -8853,7 +8675,7 @@
       </c>
       <c r="E134" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101128X</v>
+        <v>121114128X</v>
       </c>
       <c r="I134" s="106"/>
     </row>
@@ -8863,7 +8685,7 @@
       </c>
       <c r="B135">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C135" s="98" t="s">
         <v>711</v>
@@ -8873,7 +8695,7 @@
       </c>
       <c r="E135" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101129A</v>
+        <v>121114129A</v>
       </c>
       <c r="I135" s="106"/>
     </row>
@@ -8883,7 +8705,7 @@
       </c>
       <c r="B136">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C136" s="98" t="s">
         <v>712</v>
@@ -8893,7 +8715,7 @@
       </c>
       <c r="E136" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101130H</v>
+        <v>121114130H</v>
       </c>
       <c r="I136" s="106"/>
     </row>
@@ -8903,7 +8725,7 @@
       </c>
       <c r="B137">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C137" s="98" t="s">
         <v>713</v>
@@ -8913,7 +8735,7 @@
       </c>
       <c r="E137" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101131K</v>
+        <v>121114131K</v>
       </c>
       <c r="I137" s="106"/>
     </row>
@@ -8923,7 +8745,7 @@
       </c>
       <c r="B138">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C138" s="98" t="s">
         <v>714</v>
@@ -8933,7 +8755,7 @@
       </c>
       <c r="E138" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101132M</v>
+        <v>121114132M</v>
       </c>
       <c r="I138" s="106"/>
     </row>
@@ -8943,7 +8765,7 @@
       </c>
       <c r="B139">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C139" s="98" t="s">
         <v>715</v>
@@ -8953,7 +8775,7 @@
       </c>
       <c r="E139" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101133N</v>
+        <v>121114133N</v>
       </c>
       <c r="I139" s="106"/>
     </row>
@@ -8963,7 +8785,7 @@
       </c>
       <c r="B140">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C140" s="98" t="s">
         <v>716</v>
@@ -8973,7 +8795,7 @@
       </c>
       <c r="E140" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101134R</v>
+        <v>121114134R</v>
       </c>
       <c r="I140" s="106"/>
     </row>
@@ -8983,7 +8805,7 @@
       </c>
       <c r="B141">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C141" s="98" t="s">
         <v>717</v>
@@ -8993,7 +8815,7 @@
       </c>
       <c r="E141" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101135V</v>
+        <v>121114135V</v>
       </c>
       <c r="I141" s="106"/>
     </row>
@@ -9003,7 +8825,7 @@
       </c>
       <c r="B142">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C142" s="98" t="s">
         <v>718</v>
@@ -9013,7 +8835,7 @@
       </c>
       <c r="E142" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101136X</v>
+        <v>121114136X</v>
       </c>
       <c r="I142" s="106"/>
     </row>
@@ -9023,7 +8845,7 @@
       </c>
       <c r="B143">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C143" s="98" t="s">
         <v>719</v>
@@ -9033,7 +8855,7 @@
       </c>
       <c r="E143" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101137A</v>
+        <v>121114137A</v>
       </c>
       <c r="I143" s="106"/>
     </row>
@@ -9043,7 +8865,7 @@
       </c>
       <c r="B144">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C144" s="98" t="s">
         <v>720</v>
@@ -9053,7 +8875,7 @@
       </c>
       <c r="E144" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101138H</v>
+        <v>121114138H</v>
       </c>
       <c r="I144" s="106"/>
     </row>
@@ -9063,7 +8885,7 @@
       </c>
       <c r="B145">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C145" s="98" t="s">
         <v>721</v>
@@ -9073,7 +8895,7 @@
       </c>
       <c r="E145" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101139K</v>
+        <v>121114139K</v>
       </c>
       <c r="I145" s="106"/>
     </row>
@@ -9083,7 +8905,7 @@
       </c>
       <c r="B146">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C146" s="98" t="s">
         <v>722</v>
@@ -9093,7 +8915,7 @@
       </c>
       <c r="E146" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101140M</v>
+        <v>121114140M</v>
       </c>
       <c r="I146" s="106"/>
     </row>
@@ -9103,7 +8925,7 @@
       </c>
       <c r="B147">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C147" s="98" t="s">
         <v>723</v>
@@ -9113,7 +8935,7 @@
       </c>
       <c r="E147" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101141N</v>
+        <v>121114141N</v>
       </c>
       <c r="I147" s="106"/>
     </row>
@@ -9123,7 +8945,7 @@
       </c>
       <c r="B148">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C148" s="98" t="s">
         <v>724</v>
@@ -9133,7 +8955,7 @@
       </c>
       <c r="E148" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101142R</v>
+        <v>121114142R</v>
       </c>
       <c r="I148" s="106"/>
     </row>
@@ -9143,7 +8965,7 @@
       </c>
       <c r="B149">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C149" s="98" t="s">
         <v>725</v>
@@ -9153,7 +8975,7 @@
       </c>
       <c r="E149" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101143V</v>
+        <v>121114143V</v>
       </c>
       <c r="I149" s="106"/>
     </row>
@@ -9163,7 +8985,7 @@
       </c>
       <c r="B150">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C150" s="98" t="s">
         <v>726</v>
@@ -9173,7 +8995,7 @@
       </c>
       <c r="E150" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101144X</v>
+        <v>121114144X</v>
       </c>
       <c r="I150" s="106"/>
     </row>
@@ -9183,7 +9005,7 @@
       </c>
       <c r="B151">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C151" s="98" t="s">
         <v>727</v>
@@ -9193,7 +9015,7 @@
       </c>
       <c r="E151" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101145A</v>
+        <v>121114145A</v>
       </c>
       <c r="I151" s="106"/>
     </row>
@@ -9203,7 +9025,7 @@
       </c>
       <c r="B152">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C152" s="98" t="s">
         <v>728</v>
@@ -9213,7 +9035,7 @@
       </c>
       <c r="E152" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101146H</v>
+        <v>121114146H</v>
       </c>
       <c r="I152" s="106"/>
     </row>
@@ -9223,7 +9045,7 @@
       </c>
       <c r="B153">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C153" s="98" t="s">
         <v>729</v>
@@ -9233,7 +9055,7 @@
       </c>
       <c r="E153" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101147K</v>
+        <v>121114147K</v>
       </c>
       <c r="I153" s="106"/>
     </row>
@@ -9243,7 +9065,7 @@
       </c>
       <c r="B154">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C154" s="98" t="s">
         <v>730</v>
@@ -9253,7 +9075,7 @@
       </c>
       <c r="E154" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101148M</v>
+        <v>121114148M</v>
       </c>
       <c r="I154" s="106"/>
     </row>
@@ -9263,7 +9085,7 @@
       </c>
       <c r="B155">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C155" s="98" t="s">
         <v>731</v>
@@ -9273,7 +9095,7 @@
       </c>
       <c r="E155" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101149N</v>
+        <v>121114149N</v>
       </c>
       <c r="I155" s="106"/>
     </row>
@@ -9283,7 +9105,7 @@
       </c>
       <c r="B156">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C156" s="98" t="s">
         <v>732</v>
@@ -9293,7 +9115,7 @@
       </c>
       <c r="E156" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101150R</v>
+        <v>121114150R</v>
       </c>
       <c r="I156" s="106"/>
     </row>
@@ -9303,7 +9125,7 @@
       </c>
       <c r="B157">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C157" s="98" t="s">
         <v>733</v>
@@ -9313,7 +9135,7 @@
       </c>
       <c r="E157" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101151V</v>
+        <v>121114151V</v>
       </c>
       <c r="I157" s="106"/>
     </row>
@@ -9323,7 +9145,7 @@
       </c>
       <c r="B158">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C158" s="98" t="s">
         <v>734</v>
@@ -9333,7 +9155,7 @@
       </c>
       <c r="E158" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101152X</v>
+        <v>121114152X</v>
       </c>
       <c r="I158" s="106"/>
     </row>
@@ -9343,7 +9165,7 @@
       </c>
       <c r="B159">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C159" s="98" t="s">
         <v>735</v>
@@ -9353,7 +9175,7 @@
       </c>
       <c r="E159" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101153A</v>
+        <v>121114153A</v>
       </c>
       <c r="I159" s="106"/>
     </row>
@@ -9363,7 +9185,7 @@
       </c>
       <c r="B160">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C160" s="98" t="s">
         <v>736</v>
@@ -9373,7 +9195,7 @@
       </c>
       <c r="E160" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101154H</v>
+        <v>121114154H</v>
       </c>
       <c r="I160" s="106"/>
     </row>
@@ -9383,7 +9205,7 @@
       </c>
       <c r="B161">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C161" s="98" t="s">
         <v>737</v>
@@ -9393,7 +9215,7 @@
       </c>
       <c r="E161" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101155K</v>
+        <v>121114155K</v>
       </c>
       <c r="I161" s="106"/>
     </row>
@@ -9403,7 +9225,7 @@
       </c>
       <c r="B162">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C162" s="98" t="s">
         <v>738</v>
@@ -9413,7 +9235,7 @@
       </c>
       <c r="E162" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101156M</v>
+        <v>121114156M</v>
       </c>
       <c r="I162" s="106"/>
     </row>
@@ -9423,7 +9245,7 @@
       </c>
       <c r="B163">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C163" s="98" t="s">
         <v>739</v>
@@ -9433,7 +9255,7 @@
       </c>
       <c r="E163" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101157N</v>
+        <v>121114157N</v>
       </c>
       <c r="I163" s="106"/>
     </row>
@@ -9443,7 +9265,7 @@
       </c>
       <c r="B164">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C164" s="98" t="s">
         <v>740</v>
@@ -9453,7 +9275,7 @@
       </c>
       <c r="E164" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101158R</v>
+        <v>121114158R</v>
       </c>
       <c r="I164" s="106"/>
     </row>
@@ -9463,7 +9285,7 @@
       </c>
       <c r="B165">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C165" s="98" t="s">
         <v>741</v>
@@ -9473,7 +9295,7 @@
       </c>
       <c r="E165" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101159V</v>
+        <v>121114159V</v>
       </c>
       <c r="I165" s="106"/>
     </row>
@@ -9483,7 +9305,7 @@
       </c>
       <c r="B166">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C166" s="98" t="s">
         <v>742</v>
@@ -9493,7 +9315,7 @@
       </c>
       <c r="E166" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101160X</v>
+        <v>121114160X</v>
       </c>
       <c r="I166" s="106"/>
     </row>
@@ -9503,7 +9325,7 @@
       </c>
       <c r="B167">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C167" s="98" t="s">
         <v>743</v>
@@ -9513,7 +9335,7 @@
       </c>
       <c r="E167" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101161A</v>
+        <v>121114161A</v>
       </c>
       <c r="I167" s="106"/>
     </row>
@@ -9523,7 +9345,7 @@
       </c>
       <c r="B168">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C168" s="98" t="s">
         <v>744</v>
@@ -9533,7 +9355,7 @@
       </c>
       <c r="E168" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101162H</v>
+        <v>121114162H</v>
       </c>
       <c r="I168" s="106"/>
     </row>
@@ -9543,7 +9365,7 @@
       </c>
       <c r="B169">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C169" s="98" t="s">
         <v>745</v>
@@ -9553,7 +9375,7 @@
       </c>
       <c r="E169" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101163K</v>
+        <v>121114163K</v>
       </c>
       <c r="I169" s="106"/>
     </row>
@@ -9563,7 +9385,7 @@
       </c>
       <c r="B170">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C170" s="98" t="s">
         <v>746</v>
@@ -9573,7 +9395,7 @@
       </c>
       <c r="E170" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101164M</v>
+        <v>121114164M</v>
       </c>
       <c r="I170" s="106"/>
     </row>
@@ -9583,7 +9405,7 @@
       </c>
       <c r="B171">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C171" s="98" t="s">
         <v>747</v>
@@ -9593,7 +9415,7 @@
       </c>
       <c r="E171" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101165N</v>
+        <v>121114165N</v>
       </c>
       <c r="I171" s="106"/>
     </row>
@@ -9603,7 +9425,7 @@
       </c>
       <c r="B172">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C172" s="98" t="s">
         <v>748</v>
@@ -9613,7 +9435,7 @@
       </c>
       <c r="E172" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101166R</v>
+        <v>121114166R</v>
       </c>
       <c r="I172" s="106"/>
     </row>
@@ -9623,7 +9445,7 @@
       </c>
       <c r="B173">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C173" s="98" t="s">
         <v>749</v>
@@ -9633,7 +9455,7 @@
       </c>
       <c r="E173" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101167V</v>
+        <v>121114167V</v>
       </c>
       <c r="I173" s="106"/>
     </row>
@@ -9643,7 +9465,7 @@
       </c>
       <c r="B174">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C174" s="98" t="s">
         <v>750</v>
@@ -9653,7 +9475,7 @@
       </c>
       <c r="E174" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101168X</v>
+        <v>121114168X</v>
       </c>
       <c r="I174" s="106"/>
     </row>
@@ -9663,7 +9485,7 @@
       </c>
       <c r="B175">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C175" s="98" t="s">
         <v>751</v>
@@ -9673,7 +9495,7 @@
       </c>
       <c r="E175" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101169A</v>
+        <v>121114169A</v>
       </c>
       <c r="I175" s="106"/>
     </row>
@@ -9683,7 +9505,7 @@
       </c>
       <c r="B176">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C176" s="98" t="s">
         <v>752</v>
@@ -9693,7 +9515,7 @@
       </c>
       <c r="E176" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101170H</v>
+        <v>121114170H</v>
       </c>
       <c r="I176" s="106"/>
     </row>
@@ -9703,7 +9525,7 @@
       </c>
       <c r="B177">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C177" s="98" t="s">
         <v>753</v>
@@ -9713,7 +9535,7 @@
       </c>
       <c r="E177" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101171K</v>
+        <v>121114171K</v>
       </c>
       <c r="I177" s="106"/>
     </row>
@@ -9723,7 +9545,7 @@
       </c>
       <c r="B178">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C178" s="98" t="s">
         <v>754</v>
@@ -9733,7 +9555,7 @@
       </c>
       <c r="E178" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101172M</v>
+        <v>121114172M</v>
       </c>
       <c r="I178" s="106"/>
     </row>
@@ -9743,7 +9565,7 @@
       </c>
       <c r="B179">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C179" s="98" t="s">
         <v>755</v>
@@ -9753,7 +9575,7 @@
       </c>
       <c r="E179" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101173N</v>
+        <v>121114173N</v>
       </c>
       <c r="I179" s="106"/>
     </row>
@@ -9763,7 +9585,7 @@
       </c>
       <c r="B180">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C180" s="98" t="s">
         <v>756</v>
@@ -9773,7 +9595,7 @@
       </c>
       <c r="E180" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101174R</v>
+        <v>121114174R</v>
       </c>
       <c r="I180" s="106"/>
     </row>
@@ -9783,7 +9605,7 @@
       </c>
       <c r="B181">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C181" s="98" t="s">
         <v>757</v>
@@ -9793,7 +9615,7 @@
       </c>
       <c r="E181" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101175V</v>
+        <v>121114175V</v>
       </c>
       <c r="I181" s="106"/>
     </row>
@@ -9803,7 +9625,7 @@
       </c>
       <c r="B182">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C182" s="98" t="s">
         <v>758</v>
@@ -9813,7 +9635,7 @@
       </c>
       <c r="E182" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101176X</v>
+        <v>121114176X</v>
       </c>
       <c r="I182" s="106"/>
     </row>
@@ -9823,7 +9645,7 @@
       </c>
       <c r="B183">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C183" s="98" t="s">
         <v>759</v>
@@ -9833,7 +9655,7 @@
       </c>
       <c r="E183" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101177A</v>
+        <v>121114177A</v>
       </c>
       <c r="I183" s="106"/>
     </row>
@@ -9843,7 +9665,7 @@
       </c>
       <c r="B184">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C184" s="98" t="s">
         <v>760</v>
@@ -9853,7 +9675,7 @@
       </c>
       <c r="E184" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101178H</v>
+        <v>121114178H</v>
       </c>
       <c r="I184" s="106"/>
     </row>
@@ -9863,7 +9685,7 @@
       </c>
       <c r="B185">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C185" s="98" t="s">
         <v>761</v>
@@ -9873,7 +9695,7 @@
       </c>
       <c r="E185" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101179K</v>
+        <v>121114179K</v>
       </c>
       <c r="I185" s="106"/>
     </row>
@@ -9883,7 +9705,7 @@
       </c>
       <c r="B186">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C186" s="98" t="s">
         <v>762</v>
@@ -9893,7 +9715,7 @@
       </c>
       <c r="E186" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101180M</v>
+        <v>121114180M</v>
       </c>
       <c r="I186" s="106"/>
     </row>
@@ -9903,7 +9725,7 @@
       </c>
       <c r="B187">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C187" s="98" t="s">
         <v>763</v>
@@ -9913,7 +9735,7 @@
       </c>
       <c r="E187" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101181N</v>
+        <v>121114181N</v>
       </c>
       <c r="I187" s="106"/>
     </row>
@@ -9923,7 +9745,7 @@
       </c>
       <c r="B188">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C188" s="98" t="s">
         <v>764</v>
@@ -9933,7 +9755,7 @@
       </c>
       <c r="E188" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101182R</v>
+        <v>121114182R</v>
       </c>
       <c r="I188" s="106"/>
     </row>
@@ -9943,7 +9765,7 @@
       </c>
       <c r="B189">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C189" s="98" t="s">
         <v>765</v>
@@ -9953,7 +9775,7 @@
       </c>
       <c r="E189" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101183V</v>
+        <v>121114183V</v>
       </c>
       <c r="I189" s="106"/>
     </row>
@@ -9963,7 +9785,7 @@
       </c>
       <c r="B190">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C190" s="98" t="s">
         <v>766</v>
@@ -9973,7 +9795,7 @@
       </c>
       <c r="E190" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101184X</v>
+        <v>121114184X</v>
       </c>
       <c r="I190" s="106"/>
     </row>
@@ -9983,7 +9805,7 @@
       </c>
       <c r="B191">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C191" s="98" t="s">
         <v>767</v>
@@ -9993,7 +9815,7 @@
       </c>
       <c r="E191" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101185A</v>
+        <v>121114185A</v>
       </c>
       <c r="I191" s="106"/>
     </row>
@@ -10003,7 +9825,7 @@
       </c>
       <c r="B192">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C192" s="98" t="s">
         <v>768</v>
@@ -10013,7 +9835,7 @@
       </c>
       <c r="E192" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101186H</v>
+        <v>121114186H</v>
       </c>
       <c r="I192" s="106"/>
     </row>
@@ -10023,7 +9845,7 @@
       </c>
       <c r="B193">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C193" s="98" t="s">
         <v>769</v>
@@ -10033,7 +9855,7 @@
       </c>
       <c r="E193" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101187K</v>
+        <v>121114187K</v>
       </c>
       <c r="I193" s="106"/>
     </row>
@@ -10043,7 +9865,7 @@
       </c>
       <c r="B194">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C194" s="98" t="s">
         <v>770</v>
@@ -10053,7 +9875,7 @@
       </c>
       <c r="E194" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101188M</v>
+        <v>121114188M</v>
       </c>
       <c r="I194" s="106"/>
     </row>
@@ -10063,7 +9885,7 @@
       </c>
       <c r="B195">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C195" s="98" t="s">
         <v>771</v>
@@ -10073,7 +9895,7 @@
       </c>
       <c r="E195" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101189N</v>
+        <v>121114189N</v>
       </c>
       <c r="I195" s="106"/>
     </row>
@@ -10083,7 +9905,7 @@
       </c>
       <c r="B196">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C196" s="98" t="s">
         <v>772</v>
@@ -10093,7 +9915,7 @@
       </c>
       <c r="E196" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101190R</v>
+        <v>121114190R</v>
       </c>
       <c r="I196" s="106"/>
     </row>
@@ -10103,7 +9925,7 @@
       </c>
       <c r="B197">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C197" s="98" t="s">
         <v>773</v>
@@ -10113,7 +9935,7 @@
       </c>
       <c r="E197" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101191V</v>
+        <v>121114191V</v>
       </c>
       <c r="I197" s="106"/>
     </row>
@@ -10123,7 +9945,7 @@
       </c>
       <c r="B198">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C198" s="98" t="s">
         <v>774</v>
@@ -10133,7 +9955,7 @@
       </c>
       <c r="E198" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101192X</v>
+        <v>121114192X</v>
       </c>
       <c r="I198" s="106"/>
     </row>
@@ -10143,7 +9965,7 @@
       </c>
       <c r="B199">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C199" s="98" t="s">
         <v>775</v>
@@ -10153,7 +9975,7 @@
       </c>
       <c r="E199" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101193A</v>
+        <v>121114193A</v>
       </c>
       <c r="I199" s="106"/>
     </row>
@@ -10163,7 +9985,7 @@
       </c>
       <c r="B200">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C200" s="98" t="s">
         <v>776</v>
@@ -10173,7 +9995,7 @@
       </c>
       <c r="E200" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101194H</v>
+        <v>121114194H</v>
       </c>
       <c r="I200" s="106"/>
     </row>
@@ -10183,7 +10005,7 @@
       </c>
       <c r="B201">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C201" s="98" t="s">
         <v>777</v>
@@ -10193,7 +10015,7 @@
       </c>
       <c r="E201" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101195K</v>
+        <v>121114195K</v>
       </c>
       <c r="I201" s="106"/>
     </row>
@@ -10203,7 +10025,7 @@
       </c>
       <c r="B202">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C202" s="98" t="s">
         <v>778</v>
@@ -10213,7 +10035,7 @@
       </c>
       <c r="E202" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101196M</v>
+        <v>121114196M</v>
       </c>
       <c r="I202" s="106"/>
     </row>
@@ -10223,7 +10045,7 @@
       </c>
       <c r="B203">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C203" s="98" t="s">
         <v>779</v>
@@ -10233,7 +10055,7 @@
       </c>
       <c r="E203" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101197N</v>
+        <v>121114197N</v>
       </c>
       <c r="I203" s="106"/>
     </row>
@@ -10243,7 +10065,7 @@
       </c>
       <c r="B204">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C204" s="98" t="s">
         <v>780</v>
@@ -10253,7 +10075,7 @@
       </c>
       <c r="E204" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101198R</v>
+        <v>121114198R</v>
       </c>
       <c r="I204" s="106"/>
     </row>
@@ -10263,7 +10085,7 @@
       </c>
       <c r="B205">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C205" s="98" t="s">
         <v>781</v>
@@ -10273,7 +10095,7 @@
       </c>
       <c r="E205" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101199V</v>
+        <v>121114199V</v>
       </c>
       <c r="I205" s="106"/>
     </row>
@@ -10283,7 +10105,7 @@
       </c>
       <c r="B206">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C206" s="98" t="s">
         <v>782</v>
@@ -10293,7 +10115,7 @@
       </c>
       <c r="E206" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101200X</v>
+        <v>121114200X</v>
       </c>
       <c r="I206" s="106"/>
     </row>
@@ -10303,7 +10125,7 @@
       </c>
       <c r="B207">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C207" s="98" t="s">
         <v>783</v>
@@ -10313,7 +10135,7 @@
       </c>
       <c r="E207" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101201A</v>
+        <v>121114201A</v>
       </c>
       <c r="I207" s="106"/>
     </row>
@@ -10323,7 +10145,7 @@
       </c>
       <c r="B208">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C208" s="98" t="s">
         <v>784</v>
@@ -10333,7 +10155,7 @@
       </c>
       <c r="E208" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101202H</v>
+        <v>121114202H</v>
       </c>
       <c r="I208" s="106"/>
     </row>
@@ -10343,7 +10165,7 @@
       </c>
       <c r="B209">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C209" s="98" t="s">
         <v>785</v>
@@ -10353,7 +10175,7 @@
       </c>
       <c r="E209" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101203K</v>
+        <v>121114203K</v>
       </c>
       <c r="I209" s="106"/>
     </row>
@@ -10363,7 +10185,7 @@
       </c>
       <c r="B210">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C210" s="98" t="s">
         <v>786</v>
@@ -10373,7 +10195,7 @@
       </c>
       <c r="E210" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101204M</v>
+        <v>121114204M</v>
       </c>
       <c r="I210" s="106"/>
     </row>
@@ -10383,7 +10205,7 @@
       </c>
       <c r="B211">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C211" s="98" t="s">
         <v>787</v>
@@ -10393,7 +10215,7 @@
       </c>
       <c r="E211" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101205N</v>
+        <v>121114205N</v>
       </c>
       <c r="I211" s="106"/>
     </row>
@@ -10403,7 +10225,7 @@
       </c>
       <c r="B212">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C212" s="98" t="s">
         <v>788</v>
@@ -10413,7 +10235,7 @@
       </c>
       <c r="E212" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101206R</v>
+        <v>121114206R</v>
       </c>
       <c r="I212" s="106"/>
     </row>
@@ -10423,7 +10245,7 @@
       </c>
       <c r="B213">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C213" s="98" t="s">
         <v>789</v>
@@ -10433,7 +10255,7 @@
       </c>
       <c r="E213" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101207V</v>
+        <v>121114207V</v>
       </c>
       <c r="I213" s="106"/>
     </row>
@@ -10443,7 +10265,7 @@
       </c>
       <c r="B214">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C214" s="98" t="s">
         <v>790</v>
@@ -10453,7 +10275,7 @@
       </c>
       <c r="E214" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101208X</v>
+        <v>121114208X</v>
       </c>
       <c r="I214" s="106"/>
     </row>
@@ -10463,7 +10285,7 @@
       </c>
       <c r="B215">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C215" s="98" t="s">
         <v>791</v>
@@ -10473,7 +10295,7 @@
       </c>
       <c r="E215" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101209A</v>
+        <v>121114209A</v>
       </c>
       <c r="I215" s="106"/>
     </row>
@@ -10483,7 +10305,7 @@
       </c>
       <c r="B216">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C216" s="98" t="s">
         <v>792</v>
@@ -10493,7 +10315,7 @@
       </c>
       <c r="E216" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101210H</v>
+        <v>121114210H</v>
       </c>
       <c r="I216" s="106"/>
     </row>
@@ -10503,7 +10325,7 @@
       </c>
       <c r="B217">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C217" s="98" t="s">
         <v>793</v>
@@ -10513,7 +10335,7 @@
       </c>
       <c r="E217" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101211K</v>
+        <v>121114211K</v>
       </c>
       <c r="I217" s="106"/>
     </row>
@@ -10523,7 +10345,7 @@
       </c>
       <c r="B218">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C218" s="98" t="s">
         <v>794</v>
@@ -10533,7 +10355,7 @@
       </c>
       <c r="E218" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101212M</v>
+        <v>121114212M</v>
       </c>
       <c r="I218" s="106"/>
     </row>
@@ -10543,7 +10365,7 @@
       </c>
       <c r="B219">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C219" s="98" t="s">
         <v>795</v>
@@ -10553,7 +10375,7 @@
       </c>
       <c r="E219" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101213N</v>
+        <v>121114213N</v>
       </c>
       <c r="I219" s="106"/>
     </row>
@@ -10563,7 +10385,7 @@
       </c>
       <c r="B220">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C220" s="98" t="s">
         <v>796</v>
@@ -10573,7 +10395,7 @@
       </c>
       <c r="E220" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101214R</v>
+        <v>121114214R</v>
       </c>
       <c r="I220" s="106"/>
     </row>
@@ -10583,7 +10405,7 @@
       </c>
       <c r="B221">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C221" s="98" t="s">
         <v>797</v>
@@ -10593,7 +10415,7 @@
       </c>
       <c r="E221" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101215V</v>
+        <v>121114215V</v>
       </c>
       <c r="I221" s="106"/>
     </row>
@@ -10603,7 +10425,7 @@
       </c>
       <c r="B222">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C222" s="98" t="s">
         <v>798</v>
@@ -10613,7 +10435,7 @@
       </c>
       <c r="E222" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101216X</v>
+        <v>121114216X</v>
       </c>
       <c r="I222" s="106"/>
     </row>
@@ -10623,7 +10445,7 @@
       </c>
       <c r="B223">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C223" s="98" t="s">
         <v>799</v>
@@ -10633,7 +10455,7 @@
       </c>
       <c r="E223" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101217A</v>
+        <v>121114217A</v>
       </c>
       <c r="I223" s="106"/>
     </row>
@@ -10643,7 +10465,7 @@
       </c>
       <c r="B224">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C224" s="98" t="s">
         <v>800</v>
@@ -10653,7 +10475,7 @@
       </c>
       <c r="E224" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101218H</v>
+        <v>121114218H</v>
       </c>
       <c r="I224" s="106"/>
     </row>
@@ -10663,7 +10485,7 @@
       </c>
       <c r="B225">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C225" s="98" t="s">
         <v>801</v>
@@ -10673,7 +10495,7 @@
       </c>
       <c r="E225" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101219K</v>
+        <v>121114219K</v>
       </c>
       <c r="I225" s="106"/>
     </row>
@@ -10683,7 +10505,7 @@
       </c>
       <c r="B226">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C226" s="98" t="s">
         <v>802</v>
@@ -10693,7 +10515,7 @@
       </c>
       <c r="E226" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101220M</v>
+        <v>121114220M</v>
       </c>
       <c r="I226" s="106"/>
     </row>
@@ -10703,7 +10525,7 @@
       </c>
       <c r="B227">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C227" s="98" t="s">
         <v>803</v>
@@ -10713,7 +10535,7 @@
       </c>
       <c r="E227" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101221N</v>
+        <v>121114221N</v>
       </c>
       <c r="I227" s="106"/>
     </row>
@@ -10723,7 +10545,7 @@
       </c>
       <c r="B228">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C228" s="98" t="s">
         <v>804</v>
@@ -10733,7 +10555,7 @@
       </c>
       <c r="E228" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101222R</v>
+        <v>121114222R</v>
       </c>
       <c r="I228" s="106"/>
     </row>
@@ -10743,7 +10565,7 @@
       </c>
       <c r="B229">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C229" s="98" t="s">
         <v>805</v>
@@ -10753,7 +10575,7 @@
       </c>
       <c r="E229" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101223V</v>
+        <v>121114223V</v>
       </c>
       <c r="I229" s="106"/>
     </row>
@@ -10763,7 +10585,7 @@
       </c>
       <c r="B230">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C230" s="98" t="s">
         <v>806</v>
@@ -10773,7 +10595,7 @@
       </c>
       <c r="E230" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101224X</v>
+        <v>121114224X</v>
       </c>
       <c r="I230" s="106"/>
     </row>
@@ -10783,7 +10605,7 @@
       </c>
       <c r="B231">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C231" s="98" t="s">
         <v>807</v>
@@ -10793,7 +10615,7 @@
       </c>
       <c r="E231" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101225A</v>
+        <v>121114225A</v>
       </c>
       <c r="I231" s="106"/>
     </row>
@@ -10803,7 +10625,7 @@
       </c>
       <c r="B232">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C232" s="98" t="s">
         <v>808</v>
@@ -10813,7 +10635,7 @@
       </c>
       <c r="E232" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101226H</v>
+        <v>121114226H</v>
       </c>
       <c r="I232" s="106"/>
     </row>
@@ -10823,7 +10645,7 @@
       </c>
       <c r="B233">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C233" s="98" t="s">
         <v>809</v>
@@ -10833,7 +10655,7 @@
       </c>
       <c r="E233" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101227K</v>
+        <v>121114227K</v>
       </c>
       <c r="I233" s="106"/>
     </row>
@@ -10843,7 +10665,7 @@
       </c>
       <c r="B234">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C234" s="98" t="s">
         <v>810</v>
@@ -10853,7 +10675,7 @@
       </c>
       <c r="E234" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101228M</v>
+        <v>121114228M</v>
       </c>
       <c r="I234" s="106"/>
     </row>
@@ -10863,7 +10685,7 @@
       </c>
       <c r="B235">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C235" s="98" t="s">
         <v>811</v>
@@ -10873,7 +10695,7 @@
       </c>
       <c r="E235" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101229N</v>
+        <v>121114229N</v>
       </c>
       <c r="I235" s="106"/>
     </row>
@@ -10883,7 +10705,7 @@
       </c>
       <c r="B236">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C236" s="98" t="s">
         <v>812</v>
@@ -10893,7 +10715,7 @@
       </c>
       <c r="E236" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101230R</v>
+        <v>121114230R</v>
       </c>
       <c r="I236" s="106"/>
     </row>
@@ -10903,7 +10725,7 @@
       </c>
       <c r="B237">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C237" s="98" t="s">
         <v>813</v>
@@ -10913,7 +10735,7 @@
       </c>
       <c r="E237" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101231V</v>
+        <v>121114231V</v>
       </c>
       <c r="I237" s="106"/>
     </row>
@@ -10923,7 +10745,7 @@
       </c>
       <c r="B238">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C238" s="98" t="s">
         <v>814</v>
@@ -10933,7 +10755,7 @@
       </c>
       <c r="E238" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101232X</v>
+        <v>121114232X</v>
       </c>
       <c r="I238" s="106"/>
     </row>
@@ -10943,7 +10765,7 @@
       </c>
       <c r="B239">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C239" s="98" t="s">
         <v>815</v>
@@ -10953,7 +10775,7 @@
       </c>
       <c r="E239" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101233A</v>
+        <v>121114233A</v>
       </c>
       <c r="I239" s="106"/>
     </row>
@@ -10963,7 +10785,7 @@
       </c>
       <c r="B240">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C240" s="98" t="s">
         <v>816</v>
@@ -10973,7 +10795,7 @@
       </c>
       <c r="E240" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101234H</v>
+        <v>121114234H</v>
       </c>
       <c r="I240" s="106"/>
     </row>
@@ -10983,7 +10805,7 @@
       </c>
       <c r="B241">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C241" s="98" t="s">
         <v>817</v>
@@ -10993,7 +10815,7 @@
       </c>
       <c r="E241" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101235K</v>
+        <v>121114235K</v>
       </c>
       <c r="I241" s="106"/>
     </row>
@@ -11003,7 +10825,7 @@
       </c>
       <c r="B242">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C242" s="98" t="s">
         <v>818</v>
@@ -11013,7 +10835,7 @@
       </c>
       <c r="E242" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101236M</v>
+        <v>121114236M</v>
       </c>
       <c r="I242" s="106"/>
     </row>
@@ -11023,7 +10845,7 @@
       </c>
       <c r="B243">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C243" s="98" t="s">
         <v>819</v>
@@ -11033,7 +10855,7 @@
       </c>
       <c r="E243" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101237N</v>
+        <v>121114237N</v>
       </c>
       <c r="I243" s="106"/>
     </row>
@@ -11043,7 +10865,7 @@
       </c>
       <c r="B244">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C244" s="98" t="s">
         <v>820</v>
@@ -11053,7 +10875,7 @@
       </c>
       <c r="E244" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101238R</v>
+        <v>121114238R</v>
       </c>
       <c r="I244" s="106"/>
     </row>
@@ -11063,7 +10885,7 @@
       </c>
       <c r="B245">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C245" s="98" t="s">
         <v>821</v>
@@ -11073,7 +10895,7 @@
       </c>
       <c r="E245" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101239V</v>
+        <v>121114239V</v>
       </c>
       <c r="I245" s="106"/>
     </row>
@@ -11083,7 +10905,7 @@
       </c>
       <c r="B246">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C246" s="98" t="s">
         <v>822</v>
@@ -11093,7 +10915,7 @@
       </c>
       <c r="E246" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101240X</v>
+        <v>121114240X</v>
       </c>
       <c r="I246" s="106"/>
     </row>
@@ -11103,7 +10925,7 @@
       </c>
       <c r="B247">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C247" s="98" t="s">
         <v>823</v>
@@ -11113,7 +10935,7 @@
       </c>
       <c r="E247" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101241A</v>
+        <v>121114241A</v>
       </c>
       <c r="I247" s="106"/>
     </row>
@@ -11123,7 +10945,7 @@
       </c>
       <c r="B248">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C248" s="98" t="s">
         <v>824</v>
@@ -11133,7 +10955,7 @@
       </c>
       <c r="E248" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101242H</v>
+        <v>121114242H</v>
       </c>
       <c r="I248" s="106"/>
     </row>
@@ -11143,7 +10965,7 @@
       </c>
       <c r="B249">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C249" s="98" t="s">
         <v>825</v>
@@ -11153,7 +10975,7 @@
       </c>
       <c r="E249" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101243K</v>
+        <v>121114243K</v>
       </c>
       <c r="I249" s="106"/>
     </row>
@@ -11163,7 +10985,7 @@
       </c>
       <c r="B250">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C250" s="98" t="s">
         <v>826</v>
@@ -11173,7 +10995,7 @@
       </c>
       <c r="E250" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101244M</v>
+        <v>121114244M</v>
       </c>
       <c r="I250" s="106"/>
     </row>
@@ -11183,7 +11005,7 @@
       </c>
       <c r="B251">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C251" s="98" t="s">
         <v>827</v>
@@ -11193,7 +11015,7 @@
       </c>
       <c r="E251" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101245N</v>
+        <v>121114245N</v>
       </c>
       <c r="I251" s="106"/>
     </row>
@@ -11203,7 +11025,7 @@
       </c>
       <c r="B252">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C252" s="98" t="s">
         <v>828</v>
@@ -11213,7 +11035,7 @@
       </c>
       <c r="E252" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101246R</v>
+        <v>121114246R</v>
       </c>
       <c r="I252" s="106"/>
     </row>
@@ -11223,7 +11045,7 @@
       </c>
       <c r="B253">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C253" s="98" t="s">
         <v>829</v>
@@ -11233,7 +11055,7 @@
       </c>
       <c r="E253" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101247V</v>
+        <v>121114247V</v>
       </c>
       <c r="I253" s="106"/>
     </row>
@@ -11243,7 +11065,7 @@
       </c>
       <c r="B254">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C254" s="98" t="s">
         <v>830</v>
@@ -11253,7 +11075,7 @@
       </c>
       <c r="E254" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101248X</v>
+        <v>121114248X</v>
       </c>
       <c r="I254" s="106"/>
     </row>
@@ -11263,7 +11085,7 @@
       </c>
       <c r="B255">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C255" s="98" t="s">
         <v>831</v>
@@ -11273,7 +11095,7 @@
       </c>
       <c r="E255" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101249A</v>
+        <v>121114249A</v>
       </c>
       <c r="I255" s="106"/>
     </row>
@@ -11283,7 +11105,7 @@
       </c>
       <c r="B256">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C256" s="98" t="s">
         <v>832</v>
@@ -11293,7 +11115,7 @@
       </c>
       <c r="E256" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101250H</v>
+        <v>121114250H</v>
       </c>
       <c r="I256" s="106"/>
     </row>
@@ -11303,7 +11125,7 @@
       </c>
       <c r="B257">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C257" s="98" t="s">
         <v>833</v>
@@ -11313,7 +11135,7 @@
       </c>
       <c r="E257" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101251K</v>
+        <v>121114251K</v>
       </c>
       <c r="I257" s="106"/>
     </row>
@@ -11323,7 +11145,7 @@
       </c>
       <c r="B258">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C258" s="98" t="s">
         <v>834</v>
@@ -11333,7 +11155,7 @@
       </c>
       <c r="E258" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101252M</v>
+        <v>121114252M</v>
       </c>
       <c r="I258" s="106"/>
     </row>
@@ -11343,7 +11165,7 @@
       </c>
       <c r="B259">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C259" s="98" t="s">
         <v>835</v>
@@ -11353,7 +11175,7 @@
       </c>
       <c r="E259" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101253N</v>
+        <v>121114253N</v>
       </c>
       <c r="I259" s="106"/>
     </row>
@@ -11363,7 +11185,7 @@
       </c>
       <c r="B260">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C260" s="98" t="s">
         <v>836</v>
@@ -11373,7 +11195,7 @@
       </c>
       <c r="E260" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101254R</v>
+        <v>121114254R</v>
       </c>
       <c r="I260" s="106"/>
     </row>
@@ -11383,7 +11205,7 @@
       </c>
       <c r="B261">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C261" s="98" t="s">
         <v>837</v>
@@ -11393,7 +11215,7 @@
       </c>
       <c r="E261" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101255V</v>
+        <v>121114255V</v>
       </c>
       <c r="I261" s="106"/>
     </row>
@@ -11403,7 +11225,7 @@
       </c>
       <c r="B262">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C262" s="98" t="s">
         <v>838</v>
@@ -11413,7 +11235,7 @@
       </c>
       <c r="E262" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101256X</v>
+        <v>121114256X</v>
       </c>
       <c r="I262" s="106"/>
     </row>
@@ -11423,7 +11245,7 @@
       </c>
       <c r="B263">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C263" s="98" t="s">
         <v>839</v>
@@ -11433,7 +11255,7 @@
       </c>
       <c r="E263" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101257A</v>
+        <v>121114257A</v>
       </c>
       <c r="I263" s="106"/>
     </row>
@@ -11443,7 +11265,7 @@
       </c>
       <c r="B264">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C264" s="98" t="s">
         <v>840</v>
@@ -11453,7 +11275,7 @@
       </c>
       <c r="E264" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101258H</v>
+        <v>121114258H</v>
       </c>
       <c r="I264" s="106"/>
     </row>
@@ -11463,7 +11285,7 @@
       </c>
       <c r="B265">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C265" s="98" t="s">
         <v>841</v>
@@ -11473,7 +11295,7 @@
       </c>
       <c r="E265" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101259K</v>
+        <v>121114259K</v>
       </c>
       <c r="I265" s="106"/>
     </row>
@@ -11483,7 +11305,7 @@
       </c>
       <c r="B266">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C266" s="98" t="s">
         <v>842</v>
@@ -11493,7 +11315,7 @@
       </c>
       <c r="E266" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101260M</v>
+        <v>121114260M</v>
       </c>
       <c r="I266" s="106"/>
     </row>
@@ -11503,7 +11325,7 @@
       </c>
       <c r="B267">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C267" s="98" t="s">
         <v>843</v>
@@ -11513,7 +11335,7 @@
       </c>
       <c r="E267" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101261N</v>
+        <v>121114261N</v>
       </c>
       <c r="I267" s="106"/>
     </row>
@@ -11523,7 +11345,7 @@
       </c>
       <c r="B268">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C268" s="98" t="s">
         <v>844</v>
@@ -11533,7 +11355,7 @@
       </c>
       <c r="E268" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101262R</v>
+        <v>121114262R</v>
       </c>
       <c r="I268" s="106"/>
     </row>
@@ -11543,7 +11365,7 @@
       </c>
       <c r="B269">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C269" s="98" t="s">
         <v>845</v>
@@ -11553,7 +11375,7 @@
       </c>
       <c r="E269" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101263V</v>
+        <v>121114263V</v>
       </c>
       <c r="I269" s="106"/>
     </row>
@@ -11563,7 +11385,7 @@
       </c>
       <c r="B270">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C270" s="98" t="s">
         <v>846</v>
@@ -11573,7 +11395,7 @@
       </c>
       <c r="E270" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101264X</v>
+        <v>121114264X</v>
       </c>
       <c r="I270" s="106"/>
     </row>
@@ -11583,7 +11405,7 @@
       </c>
       <c r="B271">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C271" s="98" t="s">
         <v>847</v>
@@ -11593,7 +11415,7 @@
       </c>
       <c r="E271" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101265A</v>
+        <v>121114265A</v>
       </c>
       <c r="I271" s="106"/>
     </row>
@@ -11603,7 +11425,7 @@
       </c>
       <c r="B272">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C272" s="98" t="s">
         <v>848</v>
@@ -11613,7 +11435,7 @@
       </c>
       <c r="E272" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101266H</v>
+        <v>121114266H</v>
       </c>
       <c r="I272" s="106"/>
     </row>
@@ -11623,7 +11445,7 @@
       </c>
       <c r="B273">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C273" s="98" t="s">
         <v>849</v>
@@ -11633,7 +11455,7 @@
       </c>
       <c r="E273" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101267K</v>
+        <v>121114267K</v>
       </c>
       <c r="I273" s="106"/>
     </row>
@@ -11643,7 +11465,7 @@
       </c>
       <c r="B274">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C274" s="98" t="s">
         <v>850</v>
@@ -11653,7 +11475,7 @@
       </c>
       <c r="E274" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101268M</v>
+        <v>121114268M</v>
       </c>
       <c r="I274" s="106"/>
     </row>
@@ -11663,7 +11485,7 @@
       </c>
       <c r="B275">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C275" s="98" t="s">
         <v>851</v>
@@ -11673,7 +11495,7 @@
       </c>
       <c r="E275" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101269N</v>
+        <v>121114269N</v>
       </c>
       <c r="I275" s="106"/>
     </row>
@@ -11683,7 +11505,7 @@
       </c>
       <c r="B276">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C276" s="98" t="s">
         <v>852</v>
@@ -11693,7 +11515,7 @@
       </c>
       <c r="E276" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101270R</v>
+        <v>121114270R</v>
       </c>
       <c r="I276" s="106"/>
     </row>
@@ -11703,7 +11525,7 @@
       </c>
       <c r="B277">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C277" s="98" t="s">
         <v>853</v>
@@ -11713,7 +11535,7 @@
       </c>
       <c r="E277" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101271V</v>
+        <v>121114271V</v>
       </c>
       <c r="I277" s="106"/>
     </row>
@@ -11723,7 +11545,7 @@
       </c>
       <c r="B278">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C278" s="98" t="s">
         <v>854</v>
@@ -11733,7 +11555,7 @@
       </c>
       <c r="E278" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101272X</v>
+        <v>121114272X</v>
       </c>
       <c r="I278" s="106"/>
     </row>
@@ -11743,7 +11565,7 @@
       </c>
       <c r="B279">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C279" s="98" t="s">
         <v>855</v>
@@ -11753,7 +11575,7 @@
       </c>
       <c r="E279" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101273A</v>
+        <v>121114273A</v>
       </c>
       <c r="I279" s="106"/>
     </row>
@@ -11763,7 +11585,7 @@
       </c>
       <c r="B280">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C280" s="98" t="s">
         <v>856</v>
@@ -11773,7 +11595,7 @@
       </c>
       <c r="E280" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101274H</v>
+        <v>121114274H</v>
       </c>
       <c r="I280" s="106"/>
     </row>
@@ -11783,7 +11605,7 @@
       </c>
       <c r="B281">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C281" s="98" t="s">
         <v>857</v>
@@ -11793,7 +11615,7 @@
       </c>
       <c r="E281" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101275K</v>
+        <v>121114275K</v>
       </c>
       <c r="I281" s="106"/>
     </row>
@@ -11803,7 +11625,7 @@
       </c>
       <c r="B282">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C282" s="98" t="s">
         <v>858</v>
@@ -11813,7 +11635,7 @@
       </c>
       <c r="E282" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101276M</v>
+        <v>121114276M</v>
       </c>
       <c r="I282" s="106"/>
     </row>
@@ -11823,7 +11645,7 @@
       </c>
       <c r="B283">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C283" s="98" t="s">
         <v>859</v>
@@ -11833,7 +11655,7 @@
       </c>
       <c r="E283" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101277N</v>
+        <v>121114277N</v>
       </c>
       <c r="I283" s="106"/>
     </row>
@@ -11843,7 +11665,7 @@
       </c>
       <c r="B284">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C284" s="98" t="s">
         <v>860</v>
@@ -11853,7 +11675,7 @@
       </c>
       <c r="E284" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101278R</v>
+        <v>121114278R</v>
       </c>
       <c r="I284" s="106"/>
     </row>
@@ -11863,7 +11685,7 @@
       </c>
       <c r="B285">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C285" s="98" t="s">
         <v>861</v>
@@ -11873,7 +11695,7 @@
       </c>
       <c r="E285" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101279V</v>
+        <v>121114279V</v>
       </c>
       <c r="I285" s="106"/>
     </row>
@@ -11883,7 +11705,7 @@
       </c>
       <c r="B286">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C286" s="98" t="s">
         <v>862</v>
@@ -11893,7 +11715,7 @@
       </c>
       <c r="E286" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101280X</v>
+        <v>121114280X</v>
       </c>
       <c r="I286" s="106"/>
     </row>
@@ -11903,7 +11725,7 @@
       </c>
       <c r="B287">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C287" s="98" t="s">
         <v>863</v>
@@ -11913,7 +11735,7 @@
       </c>
       <c r="E287" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101281A</v>
+        <v>121114281A</v>
       </c>
       <c r="I287" s="106"/>
     </row>
@@ -11923,7 +11745,7 @@
       </c>
       <c r="B288">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C288" s="98" t="s">
         <v>864</v>
@@ -11933,7 +11755,7 @@
       </c>
       <c r="E288" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101282H</v>
+        <v>121114282H</v>
       </c>
       <c r="I288" s="106"/>
     </row>
@@ -11943,7 +11765,7 @@
       </c>
       <c r="B289">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C289" s="98" t="s">
         <v>865</v>
@@ -11953,7 +11775,7 @@
       </c>
       <c r="E289" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101283K</v>
+        <v>121114283K</v>
       </c>
       <c r="I289" s="106"/>
     </row>
@@ -11963,7 +11785,7 @@
       </c>
       <c r="B290">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C290" s="98" t="s">
         <v>866</v>
@@ -11973,7 +11795,7 @@
       </c>
       <c r="E290" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101284M</v>
+        <v>121114284M</v>
       </c>
       <c r="I290" s="106"/>
     </row>
@@ -11983,7 +11805,7 @@
       </c>
       <c r="B291">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C291" s="98" t="s">
         <v>867</v>
@@ -11993,7 +11815,7 @@
       </c>
       <c r="E291" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101285N</v>
+        <v>121114285N</v>
       </c>
       <c r="I291" s="106"/>
     </row>
@@ -12003,7 +11825,7 @@
       </c>
       <c r="B292">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C292" s="98" t="s">
         <v>868</v>
@@ -12013,7 +11835,7 @@
       </c>
       <c r="E292" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101286R</v>
+        <v>121114286R</v>
       </c>
       <c r="I292" s="106"/>
     </row>
@@ -12023,7 +11845,7 @@
       </c>
       <c r="B293">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C293" s="98" t="s">
         <v>869</v>
@@ -12033,7 +11855,7 @@
       </c>
       <c r="E293" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101287V</v>
+        <v>121114287V</v>
       </c>
       <c r="I293" s="106"/>
     </row>
@@ -12043,7 +11865,7 @@
       </c>
       <c r="B294">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C294" s="98" t="s">
         <v>870</v>
@@ -12053,7 +11875,7 @@
       </c>
       <c r="E294" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101288X</v>
+        <v>121114288X</v>
       </c>
       <c r="I294" s="106"/>
     </row>
@@ -12063,7 +11885,7 @@
       </c>
       <c r="B295">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C295" s="98" t="s">
         <v>871</v>
@@ -12073,7 +11895,7 @@
       </c>
       <c r="E295" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101289A</v>
+        <v>121114289A</v>
       </c>
       <c r="I295" s="106"/>
     </row>
@@ -12083,7 +11905,7 @@
       </c>
       <c r="B296">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C296" s="98" t="s">
         <v>872</v>
@@ -12093,7 +11915,7 @@
       </c>
       <c r="E296" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101290H</v>
+        <v>121114290H</v>
       </c>
       <c r="I296" s="106"/>
     </row>
@@ -12103,7 +11925,7 @@
       </c>
       <c r="B297">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C297" s="98" t="s">
         <v>873</v>
@@ -12113,7 +11935,7 @@
       </c>
       <c r="E297" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101291K</v>
+        <v>121114291K</v>
       </c>
       <c r="I297" s="106"/>
     </row>
@@ -12123,7 +11945,7 @@
       </c>
       <c r="B298">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C298" s="98" t="s">
         <v>874</v>
@@ -12133,7 +11955,7 @@
       </c>
       <c r="E298" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101292M</v>
+        <v>121114292M</v>
       </c>
       <c r="I298" s="106"/>
     </row>
@@ -12143,7 +11965,7 @@
       </c>
       <c r="B299">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C299" s="98" t="s">
         <v>875</v>
@@ -12153,7 +11975,7 @@
       </c>
       <c r="E299" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101293N</v>
+        <v>121114293N</v>
       </c>
       <c r="I299" s="106"/>
     </row>
@@ -12163,7 +11985,7 @@
       </c>
       <c r="B300">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C300" s="98" t="s">
         <v>876</v>
@@ -12173,7 +11995,7 @@
       </c>
       <c r="E300" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101294R</v>
+        <v>121114294R</v>
       </c>
       <c r="I300" s="106"/>
     </row>
@@ -12183,7 +12005,7 @@
       </c>
       <c r="B301">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C301" s="98" t="s">
         <v>877</v>
@@ -12193,7 +12015,7 @@
       </c>
       <c r="E301" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101295V</v>
+        <v>121114295V</v>
       </c>
       <c r="I301" s="106"/>
     </row>
@@ -12203,7 +12025,7 @@
       </c>
       <c r="B302">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C302" s="98" t="s">
         <v>878</v>
@@ -12213,7 +12035,7 @@
       </c>
       <c r="E302" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101296X</v>
+        <v>121114296X</v>
       </c>
       <c r="I302" s="106"/>
     </row>
@@ -12223,7 +12045,7 @@
       </c>
       <c r="B303">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C303" s="98" t="s">
         <v>879</v>
@@ -12233,7 +12055,7 @@
       </c>
       <c r="E303" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101297A</v>
+        <v>121114297A</v>
       </c>
       <c r="I303" s="106"/>
     </row>
@@ -12243,7 +12065,7 @@
       </c>
       <c r="B304">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C304" s="98" t="s">
         <v>880</v>
@@ -12253,7 +12075,7 @@
       </c>
       <c r="E304" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101298H</v>
+        <v>121114298H</v>
       </c>
       <c r="I304" s="106"/>
     </row>
@@ -12263,7 +12085,7 @@
       </c>
       <c r="B305">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C305" s="98" t="s">
         <v>881</v>
@@ -12273,7 +12095,7 @@
       </c>
       <c r="E305" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101299K</v>
+        <v>121114299K</v>
       </c>
       <c r="I305" s="106"/>
     </row>
@@ -12283,7 +12105,7 @@
       </c>
       <c r="B306">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C306" s="98" t="s">
         <v>882</v>
@@ -12293,7 +12115,7 @@
       </c>
       <c r="E306" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101300M</v>
+        <v>121114300M</v>
       </c>
       <c r="I306" s="106"/>
     </row>
@@ -12303,7 +12125,7 @@
       </c>
       <c r="B307">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C307" s="98" t="s">
         <v>883</v>
@@ -12313,7 +12135,7 @@
       </c>
       <c r="E307" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101301N</v>
+        <v>121114301N</v>
       </c>
       <c r="I307" s="106"/>
     </row>
@@ -12323,7 +12145,7 @@
       </c>
       <c r="B308">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C308" s="98" t="s">
         <v>884</v>
@@ -12333,7 +12155,7 @@
       </c>
       <c r="E308" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101302R</v>
+        <v>121114302R</v>
       </c>
       <c r="I308" s="106"/>
     </row>
@@ -12343,7 +12165,7 @@
       </c>
       <c r="B309">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C309" s="98" t="s">
         <v>885</v>
@@ -12353,7 +12175,7 @@
       </c>
       <c r="E309" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101303V</v>
+        <v>121114303V</v>
       </c>
       <c r="I309" s="106"/>
     </row>
@@ -12363,7 +12185,7 @@
       </c>
       <c r="B310">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C310" s="98" t="s">
         <v>886</v>
@@ -12373,7 +12195,7 @@
       </c>
       <c r="E310" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101304X</v>
+        <v>121114304X</v>
       </c>
       <c r="I310" s="106"/>
     </row>
@@ -12383,7 +12205,7 @@
       </c>
       <c r="B311">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C311" s="98" t="s">
         <v>887</v>
@@ -12393,7 +12215,7 @@
       </c>
       <c r="E311" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101305A</v>
+        <v>121114305A</v>
       </c>
       <c r="I311" s="106"/>
     </row>
@@ -12403,7 +12225,7 @@
       </c>
       <c r="B312">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C312" s="98" t="s">
         <v>888</v>
@@ -12413,7 +12235,7 @@
       </c>
       <c r="E312" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101306H</v>
+        <v>121114306H</v>
       </c>
       <c r="I312" s="106"/>
     </row>
@@ -12423,7 +12245,7 @@
       </c>
       <c r="B313">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C313" s="98" t="s">
         <v>889</v>
@@ -12433,7 +12255,7 @@
       </c>
       <c r="E313" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101307K</v>
+        <v>121114307K</v>
       </c>
       <c r="I313" s="106"/>
     </row>
@@ -12443,7 +12265,7 @@
       </c>
       <c r="B314">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C314" s="98" t="s">
         <v>890</v>
@@ -12453,7 +12275,7 @@
       </c>
       <c r="E314" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101308M</v>
+        <v>121114308M</v>
       </c>
       <c r="I314" s="106"/>
     </row>
@@ -12463,7 +12285,7 @@
       </c>
       <c r="B315">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C315" s="98" t="s">
         <v>891</v>
@@ -12473,7 +12295,7 @@
       </c>
       <c r="E315" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101309N</v>
+        <v>121114309N</v>
       </c>
       <c r="I315" s="106"/>
     </row>
@@ -12483,7 +12305,7 @@
       </c>
       <c r="B316">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C316" s="98" t="s">
         <v>892</v>
@@ -12493,7 +12315,7 @@
       </c>
       <c r="E316" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101310R</v>
+        <v>121114310R</v>
       </c>
       <c r="I316" s="106"/>
     </row>
@@ -12503,7 +12325,7 @@
       </c>
       <c r="B317">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C317" s="98" t="s">
         <v>893</v>
@@ -12513,7 +12335,7 @@
       </c>
       <c r="E317" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101311V</v>
+        <v>121114311V</v>
       </c>
       <c r="I317" s="106"/>
     </row>
@@ -12523,7 +12345,7 @@
       </c>
       <c r="B318">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C318" s="98" t="s">
         <v>894</v>
@@ -12533,7 +12355,7 @@
       </c>
       <c r="E318" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101312X</v>
+        <v>121114312X</v>
       </c>
       <c r="I318" s="106"/>
     </row>
@@ -12543,7 +12365,7 @@
       </c>
       <c r="B319">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C319" s="98" t="s">
         <v>895</v>
@@ -12553,7 +12375,7 @@
       </c>
       <c r="E319" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101313A</v>
+        <v>121114313A</v>
       </c>
       <c r="I319" s="106"/>
     </row>
@@ -12563,7 +12385,7 @@
       </c>
       <c r="B320">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C320" s="98" t="s">
         <v>896</v>
@@ -12573,7 +12395,7 @@
       </c>
       <c r="E320" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101314H</v>
+        <v>121114314H</v>
       </c>
       <c r="I320" s="106"/>
     </row>
@@ -12583,7 +12405,7 @@
       </c>
       <c r="B321">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C321" s="98" t="s">
         <v>897</v>
@@ -12593,7 +12415,7 @@
       </c>
       <c r="E321" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101315K</v>
+        <v>121114315K</v>
       </c>
       <c r="I321" s="106"/>
     </row>
@@ -12603,7 +12425,7 @@
       </c>
       <c r="B322">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C322" s="98" t="s">
         <v>898</v>
@@ -12613,7 +12435,7 @@
       </c>
       <c r="E322" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101316M</v>
+        <v>121114316M</v>
       </c>
       <c r="I322" s="106"/>
     </row>
@@ -12623,7 +12445,7 @@
       </c>
       <c r="B323">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C323" s="98" t="s">
         <v>899</v>
@@ -12633,7 +12455,7 @@
       </c>
       <c r="E323" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101317N</v>
+        <v>121114317N</v>
       </c>
       <c r="I323" s="106"/>
     </row>
@@ -12643,7 +12465,7 @@
       </c>
       <c r="B324">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C324" s="98" t="s">
         <v>900</v>
@@ -12653,7 +12475,7 @@
       </c>
       <c r="E324" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101318R</v>
+        <v>121114318R</v>
       </c>
       <c r="I324" s="106"/>
     </row>
@@ -12663,7 +12485,7 @@
       </c>
       <c r="B325">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C325" s="98" t="s">
         <v>901</v>
@@ -12673,7 +12495,7 @@
       </c>
       <c r="E325" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101319V</v>
+        <v>121114319V</v>
       </c>
       <c r="I325" s="106"/>
     </row>
@@ -12683,7 +12505,7 @@
       </c>
       <c r="B326">
         <f ca="1">設定!$A$14</f>
-        <v>110101</v>
+        <v>121114</v>
       </c>
       <c r="C326" s="98" t="s">
         <v>902</v>
@@ -12693,7 +12515,7 @@
       </c>
       <c r="E326" s="106" t="str">
         <f ca="1">テーブル3[[#This Row],[学校コード]]&amp;テーブル3[[#This Row],[数字]]&amp;テーブル3[[#This Row],[記号2]]</f>
-        <v>110101320X</v>
+        <v>121114320X</v>
       </c>
       <c r="F326" s="107"/>
       <c r="G326" s="107"/>
